--- a/Supplementary_Table_1_Data_Dictionary_v1.0.xlsx
+++ b/Supplementary_Table_1_Data_Dictionary_v1.0.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="22188" windowHeight="9060" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Supplementary Table 1" sheetId="1" r:id="rId1"/>
@@ -28,12 +28,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="699" uniqueCount="380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="634" uniqueCount="357">
   <si>
     <t>Supplementary Table 1. Data dictionary and code definitions for the seasonal frozen-ground strong-motion flatfile.</t>
   </si>
   <si>
-    <t>Schema documented for the current flatfile: Seasonal_Frozen_Ground_Strong_Motion_Database.xlsx</t>
+    <t>Schema for the 54-field flatfile: Seasonal_Frozen_Ground_Strong_Motion_Database.csv</t>
   </si>
   <si>
     <t>Each row corresponds to one released flatfile field, using the exact field name and column order.</t>
@@ -123,7 +123,7 @@
     <t>Event times from different data sources are standardized and matched exactly.</t>
   </si>
   <si>
-    <t>YYYY-MM-DD HH:MM:SS</t>
+    <t>YYYY/M/D H:MM (e.g., 2016/1/3 9:37)</t>
   </si>
   <si>
     <t>Only records with identical standardized event times are linked across data sources.</t>
@@ -189,7 +189,7 @@
     <t>Derived from F-net source-mechanism information, focal depth, and subducting-slab geometry.</t>
   </si>
   <si>
-    <t>The classification uses TOF(P-T axes), source depth relative to the slab interface, and nodal-plane dip relative to the slab-interface dip.</t>
+    <t>The classification uses TOF(P-T axes), source depth relative to the slab interface, and the dip difference between the identified rupture plane and the slab interface.</t>
   </si>
   <si>
     <t>Shallow_crustal; Upper_mantle; Interface; Intraslab; Unknown</t>
@@ -210,10 +210,10 @@
     <t>F-net P- and T-axis parameters.</t>
   </si>
   <si>
-    <t>Classified from the reported P- and T-axis plunge angles. Events with T-axis plunge &gt; 40° are classified as R, those with P-axis plunge &gt; 40° are classified as N, and the remaining events are classified as S.</t>
-  </si>
-  <si>
-    <t>S = strike-slip; N = normal-fault; R = reverse/thrust</t>
+    <t>Events with a T-axis plunge &gt; 40° are classified as R, those with a P-axis plunge &gt; 40° as N, and those with both plunges ≤ 40° as S. Cases without a unique classification or valid axis parameters are coded Unknown.</t>
+  </si>
+  <si>
+    <t>S = strike-slip; N = normal-fault; R = reverse/thrust; Unknown = unclassified or unavailable</t>
   </si>
   <si>
     <t>This field is an input to Tectonic type(zhao). It is not directly used after the final tectonic type has been assigned.</t>
@@ -222,120 +222,72 @@
     <t>H</t>
   </si>
   <si>
-    <t>TOF(rake)</t>
-  </si>
-  <si>
-    <t>Event-scale faulting type determined from the rake angles of the two F-net nodal planes.</t>
-  </si>
-  <si>
-    <t>F-net focal-mechanism solution.</t>
-  </si>
-  <si>
-    <t>Each F-net nodal plane is classified as TF for rake angles from 45° to 135°, NF for rake angles from −135° to −45°, and SS otherwise. If the two plane-level classifications do not yield a unique event-scale result, or if valid rake parameters are unavailable, the value is recorded as Unknown.</t>
-  </si>
-  <si>
-    <t>SS = strike-slip; NF = normal; TF = thrust/reverse; Unknown = indeterminate</t>
-  </si>
-  <si>
-    <t>Unknown is a valid faulting-type code and is not treated as a missing value. TOF(rake) is not used in the current Rrup calculation.</t>
+    <t>M</t>
+  </si>
+  <si>
+    <t>JMA catalogue magnitude (Mj).</t>
+  </si>
+  <si>
+    <t>NIED/JMA event catalogue.</t>
+  </si>
+  <si>
+    <t>Magnitude</t>
   </si>
   <si>
     <t>I</t>
   </si>
   <si>
-    <t>M</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2937"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>JMA catalogue magnitude (M</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="subscript"/>
-        <sz val="10"/>
-        <color rgb="FF1F2937"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>j</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2937"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>).</t>
-    </r>
-  </si>
-  <si>
-    <t>NIED/JMA event catalogue.</t>
-  </si>
-  <si>
-    <t>Magnitude</t>
-  </si>
-  <si>
-    <t/>
+    <t>Mw</t>
+  </si>
+  <si>
+    <t>Moment magnitude (Mw).</t>
+  </si>
+  <si>
+    <t>F-net moment tensor catalogue.</t>
+  </si>
+  <si>
+    <t>4.0 ≤ Mw ≤ 6.5</t>
+  </si>
+  <si>
+    <t>PART II: Recording site and seasonal frozen ground parameters</t>
   </si>
   <si>
     <t>J</t>
   </si>
   <si>
-    <t>Mw</t>
-  </si>
-  <si>
-    <t>Moment magnitude (Mw).</t>
-  </si>
-  <si>
-    <t>F-net moment tensor catalogue.</t>
-  </si>
-  <si>
-    <t>4.0 ≤ Mw ≤ 6.5</t>
-  </si>
-  <si>
-    <t>PART II: Station and freeze–thaw metadata</t>
+    <t>Network</t>
+  </si>
+  <si>
+    <t>Strong-motion network providing the record.</t>
+  </si>
+  <si>
+    <t>KiK-net record metadata.</t>
+  </si>
+  <si>
+    <t>Direct metadata value.</t>
+  </si>
+  <si>
+    <t>KiK-net</t>
   </si>
   <si>
     <t>K</t>
   </si>
   <si>
-    <t>Network</t>
-  </si>
-  <si>
-    <t>Strong-motion network providing the record.</t>
-  </si>
-  <si>
-    <t>KiK-net record metadata.</t>
-  </si>
-  <si>
-    <t>Direct metadata value.</t>
-  </si>
-  <si>
-    <t>KiK-net</t>
+    <t>Si code</t>
+  </si>
+  <si>
+    <t>Strong-motion station code.</t>
+  </si>
+  <si>
+    <t>KiK-net station metadata.</t>
+  </si>
+  <si>
+    <t>Example: KYTH03</t>
   </si>
   <si>
     <t>L</t>
   </si>
   <si>
-    <t>Si code</t>
-  </si>
-  <si>
-    <t>Strong-motion station code.</t>
-  </si>
-  <si>
-    <t>KiK-net station metadata.</t>
-  </si>
-  <si>
-    <t>Example: KYTH03</t>
-  </si>
-  <si>
     <t>Si name</t>
   </si>
   <si>
@@ -345,696 +297,612 @@
     <t>Example: FUKUCHIYAMA</t>
   </si>
   <si>
+    <t>city</t>
+  </si>
+  <si>
+    <t>Prefecture-level administrative unit of the station.</t>
+  </si>
+  <si>
+    <t>Station-location metadata compiled for the flatfile.</t>
+  </si>
+  <si>
+    <t>Assigned from station location.</t>
+  </si>
+  <si>
+    <t>Japanese prefecture name</t>
+  </si>
+  <si>
     <t>N</t>
   </si>
   <si>
-    <t>city</t>
-  </si>
-  <si>
-    <t>Prefecture-level administrative unit of the station.</t>
-  </si>
-  <si>
-    <t>Station-location metadata compiled for the flatfile.</t>
-  </si>
-  <si>
-    <t>Assigned from station location.</t>
-  </si>
-  <si>
-    <t>Japanese prefecture name</t>
+    <t>City/Municipality</t>
+  </si>
+  <si>
+    <t>City or municipality of the station.</t>
+  </si>
+  <si>
+    <t>Japanese city/municipality name</t>
   </si>
   <si>
     <t>O</t>
   </si>
   <si>
-    <t>City/Municipality</t>
-  </si>
-  <si>
-    <t>City or municipality of the station.</t>
-  </si>
-  <si>
-    <t>Japanese city/municipality name</t>
+    <t>long_st</t>
+  </si>
+  <si>
+    <t>Longitude of the strong-motion station.</t>
   </si>
   <si>
     <t>P</t>
   </si>
   <si>
-    <t>long_st</t>
-  </si>
-  <si>
-    <t>Longitude of the strong-motion station.</t>
+    <t>lat_st</t>
+  </si>
+  <si>
+    <t>Latitude of the strong-motion station.</t>
   </si>
   <si>
     <t>Q</t>
   </si>
   <si>
-    <t>lat_st</t>
-  </si>
-  <si>
-    <t>Latitude of the strong-motion station.</t>
+    <t>st ele</t>
+  </si>
+  <si>
+    <t>Terrain elevation at the strong-motion station location.</t>
+  </si>
+  <si>
+    <t>m</t>
+  </si>
+  <si>
+    <t>GEBCO_2025 Grid.</t>
+  </si>
+  <si>
+    <t>Extracted from the GEBCO_2025 Grid at the strong-motion station coordinates.</t>
+  </si>
+  <si>
+    <t>Continuous value; negative elevations are permitted.</t>
   </si>
   <si>
     <t>R</t>
   </si>
   <si>
-    <t>st ele</t>
-  </si>
-  <si>
-    <t>Terrain elevation at the strong-motion station location.</t>
-  </si>
-  <si>
-    <t>m</t>
-  </si>
-  <si>
-    <t>GEBCO_2025 Grid.</t>
-  </si>
-  <si>
-    <t>Extracted from the GEBCO_2025 Grid at the strong-motion station coordinates.</t>
-  </si>
-  <si>
-    <t>Continuous value; negative elevations are permitted.</t>
+    <t>FI</t>
+  </si>
+  <si>
+    <t>Multi-year mean air freezing index at the meteorological station matched to the strong-motion station.</t>
+  </si>
+  <si>
+    <t>°C·d</t>
+  </si>
+  <si>
+    <t>JMA daily mean air temperature.</t>
+  </si>
+  <si>
+    <t>Annual freezing indices are calculated separately for each complete year from 2016 to 2024 using daily mean temperatures below 0 °C and are then averaged across the nine years.</t>
+  </si>
+  <si>
+    <t>Non-negative value</t>
+  </si>
+  <si>
+    <t>The annual freezing index is the cumulative absolute value of daily mean temperatures below 0 °C.</t>
   </si>
   <si>
     <t>S</t>
   </si>
   <si>
-    <t>FI</t>
-  </si>
-  <si>
-    <t>Multi-year mean air freezing index at the meteorological station matched to the strong-motion station.</t>
-  </si>
-  <si>
-    <t>°C·d</t>
-  </si>
-  <si>
-    <t>JMA daily mean air temperature.</t>
-  </si>
-  <si>
-    <t>Annual freezing indices are calculated separately for each complete year from 2016 to 2024 using daily mean temperatures below 0 °C and are then averaged across the nine years.</t>
-  </si>
-  <si>
-    <t>Non-negative value</t>
-  </si>
-  <si>
-    <t>The annual freezing index is the cumulative absolute value of daily mean temperatures below 0 °C.</t>
+    <t>Ea</t>
+  </si>
+  <si>
+    <t>Geographic coefficient used in the modified Stefan formulation for estimating standard-site frost depth.</t>
+  </si>
+  <si>
+    <t>cm·(°C·d)^−1/2</t>
+  </si>
+  <si>
+    <t>Wang et al. (2024).</t>
+  </si>
+  <si>
+    <t>Calculated from station latitude, longitude, and elevation using the general-region empirical relationship.</t>
+  </si>
+  <si>
+    <t>Continuous value</t>
+  </si>
+  <si>
+    <t>The original empirical relationship was developed for standard sites in China and is applied here as a regional extrapolation.</t>
   </si>
   <si>
     <t>T</t>
   </si>
   <si>
-    <t>Ea</t>
-  </si>
-  <si>
-    <t>Geographic coefficient used in the modified Stefan formulation for estimating standard-site frost depth.</t>
-  </si>
-  <si>
-    <t>cm·(°C·d)^−1/2</t>
-  </si>
-  <si>
-    <t>Wang et al. (2024).</t>
-  </si>
-  <si>
-    <t>Calculated from station latitude, longitude, and elevation using the general-region empirical relationship.</t>
-  </si>
-  <si>
-    <t>Continuous value</t>
-  </si>
-  <si>
-    <t>The original empirical relationship was developed for standard sites in China and is applied here as a regional extrapolation.</t>
+    <t>ξ</t>
+  </si>
+  <si>
+    <t>Estimated station-scale standard-site frost depth.</t>
+  </si>
+  <si>
+    <t>cm</t>
+  </si>
+  <si>
+    <t>Derived from Ea and the air freezing index.</t>
+  </si>
+  <si>
+    <t>Calculated as ξ = Ea√FI; the resulting value is stored in centimetres.</t>
+  </si>
+  <si>
+    <t>This field is an estimated environmental annotation rather than an in-situ measured frost depth.</t>
   </si>
   <si>
     <t>U</t>
   </si>
   <si>
-    <t>ξ</t>
-  </si>
-  <si>
-    <t>Estimated station-scale standard-site frost depth.</t>
-  </si>
-  <si>
-    <t>cm</t>
-  </si>
-  <si>
-    <t>Derived from Ea and the air freezing index.</t>
-  </si>
-  <si>
-    <t>Calculated as ξ = Ea√FI; the resulting value is stored in centimetres.</t>
-  </si>
-  <si>
-    <t>This field is an estimated environmental annotation rather than an in-situ measured frost depth.</t>
+    <t>freeze_thaw_state</t>
+  </si>
+  <si>
+    <t>Record-level ground-freezing status assigned for the event date.</t>
+  </si>
+  <si>
+    <t>0/1 code</t>
+  </si>
+  <si>
+    <t>Integer</t>
+  </si>
+  <si>
+    <t>Calculated from the mean daily air temperature of the day before, the event day, and the day after the event. A record is classified as frozen when the three-day mean temperature is &lt; 0 °C and as non-frozen otherwise. For 36 records without a complete three-day temperature window, the event-day mean temperature is used.</t>
+  </si>
+  <si>
+    <t>0 = non-frozen; 1 = frozen</t>
+  </si>
+  <si>
+    <t>The three-day mean temperature is used for 34,618 records. For the remaining 36 records, ground-freezing status is determined from the event-day mean temperature using the same 0 °C threshold.</t>
   </si>
   <si>
     <t>V</t>
   </si>
   <si>
-    <t>freeze_thaw_state</t>
-  </si>
-  <si>
-    <t>Record-level ground-freezing status assigned for the event date.</t>
-  </si>
-  <si>
-    <t>0/1 code</t>
-  </si>
-  <si>
-    <t>Integer</t>
-  </si>
-  <si>
-    <t>Calculated from the mean daily air temperature of the day before, the event day, and the day after the event. A record is classified as frozen when the three-day mean temperature is &lt; 0 °C and as non-frozen otherwise. For 36 records without a complete three-day temperature window, the event-day mean temperature is used.</t>
-  </si>
-  <si>
-    <t>0 = non-frozen; 1 = frozen</t>
-  </si>
-  <si>
-    <t>The three-day mean temperature is used for 34,618 records. For the remaining 36 records, ground-freezing status is determined from the event-day mean temperature using the same 0 °C threshold.</t>
+    <t>distance_to_weather_station</t>
+  </si>
+  <si>
+    <t>Surface distance between the strong-motion station and the matched meteorological station.</t>
+  </si>
+  <si>
+    <t>KiK-net station coordinates and JMA meteorological-station coordinates.</t>
+  </si>
+  <si>
+    <t>Calculated with the Haversine great-circle formula; the nearest meteorological station is selected.</t>
+  </si>
+  <si>
+    <t>0–30 km</t>
+  </si>
+  <si>
+    <t>The maximum allowed matching distance is 30 km.</t>
   </si>
   <si>
     <t>W</t>
   </si>
   <si>
-    <t>freeze_thaw_cycle_count</t>
-  </si>
-  <si>
-    <t>Multi-year mean annual number of freeze–thaw temperature-state transitions at the matched meteorological station.</t>
-  </si>
-  <si>
-    <t>transitions·yr−1</t>
-  </si>
-  <si>
-    <t>For each complete year from 2016 to 2024, daily mean temperatures are classified as below 0 °C or not below 0 °C. A transition between the two states on consecutive days is counted once, and the annual transition counts are averaged across the nine years.</t>
-  </si>
-  <si>
-    <t>This field counts temperature-state transitions and does not necessarily represent complete closed freeze–thaw cycles.</t>
+    <t>Vs30</t>
+  </si>
+  <si>
+    <t>Time-averaged shear-wave velocity in the upper 30 m.</t>
+  </si>
+  <si>
+    <t>m·s−1</t>
+  </si>
+  <si>
+    <t>KiK-net shear-wave velocity profile.</t>
+  </si>
+  <si>
+    <t>Calculated as the travel-time average after truncating the profile to the upper 30 m.</t>
+  </si>
+  <si>
+    <t>Positive value</t>
+  </si>
+  <si>
+    <t>Vs30 was calculated only for stations with shear-wave velocity profiles extending to at least 30 m below the ground surface. Profiles shallower than 30 m were excluded, and no extrapolation was performed.</t>
   </si>
   <si>
     <t>X</t>
   </si>
   <si>
-    <t>distance_to_weather_station</t>
-  </si>
-  <si>
-    <t>Surface distance between the strong-motion station and the matched meteorological station.</t>
-  </si>
-  <si>
-    <t>KiK-net station coordinates and JMA meteorological-station coordinates.</t>
-  </si>
-  <si>
-    <t>Calculated with the Haversine great-circle formula; the nearest meteorological station is selected.</t>
-  </si>
-  <si>
-    <t>0–30 km</t>
-  </si>
-  <si>
-    <t>The maximum allowed matching distance is 30 km.</t>
+    <t>site class(JP)</t>
+  </si>
+  <si>
+    <t>Japanese site-class code based on the station fundamental site period.</t>
+  </si>
+  <si>
+    <t>Station fundamental site period.</t>
+  </si>
+  <si>
+    <t>Assigned using the station fundamental site period following the adopted Japanese site-classification scheme.</t>
+  </si>
+  <si>
+    <t>HR; SCI; SCII; SCIII; SCIV</t>
+  </si>
+  <si>
+    <t>The category codes follow the Japanese site classification scheme adopted in this study. A value of −999 indicates that the site class could not be determined reliably.</t>
+  </si>
+  <si>
+    <t>PART III: Source-to-site distance metrics</t>
   </si>
   <si>
     <t>Y</t>
   </si>
   <si>
-    <t>Vs30</t>
-  </si>
-  <si>
-    <t>Time-averaged shear-wave velocity in the upper 30 m.</t>
-  </si>
-  <si>
-    <t>m·s−1</t>
-  </si>
-  <si>
-    <t>KiK-net shear-wave velocity profile.</t>
-  </si>
-  <si>
-    <t>Calculated as the travel-time average after truncating the profile to the upper 30 m.</t>
-  </si>
-  <si>
-    <t>Positive value</t>
-  </si>
-  <si>
-    <t>Vs30 was calculated only for stations with shear-wave velocity profiles extending to at least 30 m below the ground surface. Profiles shallower than 30 m were excluded, and no extrapolation was performed.</t>
+    <t>Repi</t>
+  </si>
+  <si>
+    <t>Epicentral distance between the earthquake epicenter and the recording station.</t>
+  </si>
+  <si>
+    <t>Event and station coordinates.</t>
+  </si>
+  <si>
+    <t>Calculated by geodesic inversion on the WGS84 ellipsoid.</t>
   </si>
   <si>
     <t>Z</t>
   </si>
   <si>
-    <t>site class(JP Vs30)</t>
-  </si>
-  <si>
-    <t>Japanese Vs30-based site-class code.</t>
-  </si>
-  <si>
-    <t>Derived from Vs30.</t>
-  </si>
-  <si>
-    <t>Assigned using the adopted Japanese Vs30-based site-classification scheme.</t>
-  </si>
-  <si>
-    <t>HR; SCI; SCII; SCIII; SCIV</t>
-  </si>
-  <si>
-    <t>The category codes follow the Japanese site classification scheme adopted in this study. A value of −999 indicates that the site class could not be determined reliably.</t>
-  </si>
-  <si>
-    <t>PART III: Source-to-site distance metrics</t>
+    <t>Rhyp</t>
+  </si>
+  <si>
+    <t>Hypocentral distance between the earthquake hypocenter and the recording station.</t>
+  </si>
+  <si>
+    <t>Repi and Depth.</t>
+  </si>
+  <si>
+    <t>Calculated as sqrt(Repi² + Depth²).</t>
+  </si>
+  <si>
+    <t>Point-source distance; it does not include rupture-plane geometry.</t>
   </si>
   <si>
     <t>AA</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF17365D"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>R</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <vertAlign val="subscript"/>
-        <sz val="10"/>
-        <color rgb="FF17365D"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>epi</t>
-    </r>
-  </si>
-  <si>
-    <t>Epicentral distance between the earthquake epicenter and the recording station.</t>
-  </si>
-  <si>
-    <t>Event and station coordinates.</t>
-  </si>
-  <si>
-    <t>Calculated by geodesic inversion on the WGS84 ellipsoid.</t>
+    <t>Rrup</t>
+  </si>
+  <si>
+    <t>Closest three-dimensional distance from the recording station to the adopted rupture surface.</t>
+  </si>
+  <si>
+    <t>NIED finite-fault models, F-net nodal-plane geometry, Mw, and Tectonic type(zhao).</t>
+  </si>
+  <si>
+    <t>For events with a publicly available finite-fault model, Rrup is calculated directly from the published rupture geometry and subfault representation; all such models adopted in this study were obtained from the NIED Source Inversion Analysis database. For events without a public model, rupture dimensions are estimated using Strasser et al. (2010) for Interface and Intraslab events and Wells and Coppersmith (1994) for Shallow_crustal events. Two candidate rupture planes are constructed from the F-net nodal-plane strike and dip values. Fifty source-location simulations are performed for each plane. The median minimum distance is retained for each plane, followed by the median of the two plane-based results.</t>
+  </si>
+  <si>
+    <t>Non-negative distance; −999 = not calculated or unavailable</t>
+  </si>
+  <si>
+    <t>For events without a publicly available finite-fault model, records classified as Upper_mantle or Unknown, or records lacking the source parameters required for empirical rupture construction, are assigned −999.</t>
+  </si>
+  <si>
+    <t>PART IV: Significant-duration measures</t>
   </si>
   <si>
     <t>AB</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF17365D"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>R</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <vertAlign val="subscript"/>
-        <sz val="10"/>
-        <color rgb="FF17365D"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>hyp</t>
-    </r>
-  </si>
-  <si>
-    <t>Hypocentral distance between the earthquake hypocenter and the recording station.</t>
-  </si>
-  <si>
-    <t>Repi and Depth.</t>
-  </si>
-  <si>
-    <t>Calculated as sqrt(Repi² + Depth²).</t>
-  </si>
-  <si>
-    <t>Point-source distance; it does not include rupture-plane geometry.</t>
+    <t>t_duration(EW)(D5_75)</t>
+  </si>
+  <si>
+    <t>Significant duration between 5% and 75% of Arias intensity for the EW component.</t>
+  </si>
+  <si>
+    <t>s</t>
+  </si>
+  <si>
+    <t>KiK-net surface acceleration record.</t>
+  </si>
+  <si>
+    <t>Calculated from the preprocessed component acceleration time history.</t>
+  </si>
+  <si>
+    <t>Computed separately for each component.</t>
   </si>
   <si>
     <t>AC</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF17365D"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>R</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <vertAlign val="subscript"/>
-        <sz val="10"/>
-        <color rgb="FF17365D"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>rup</t>
-    </r>
-  </si>
-  <si>
-    <t>Closest three-dimensional distance from the recording station to the adopted rupture surface.</t>
-  </si>
-  <si>
-    <t>NIED finite-fault models, F-net nodal-plane geometry, Mw, and Tectonic type(zhao).</t>
-  </si>
-  <si>
-    <t>For events with a publicly available finite-fault model, Rrup is calculated directly from the published rupture geometry and subfault representation; all such models adopted in this study were obtained from the NIED Source Inversion Analysis database. For events without a public model, rupture dimensions are estimated using Strasser et al. (2010) for Interface and Intraslab events and Wells and Coppersmith (1994) for Shallow_crustal events. Two candidate rupture planes are constructed from the F-net nodal-plane strike and dip values. Fifty source-location simulations are performed for each plane. The median minimum distance is retained for each plane, followed by the median of the two plane-based results.</t>
-  </si>
-  <si>
-    <t>Non-negative distance; −999 = not calculated or unavailable</t>
-  </si>
-  <si>
-    <t>For events without a publicly available finite-fault model, records classified as Upper_mantle or Unknown, or records lacking the source parameters required for empirical rupture construction, are assigned −999. TOF(rake) is not used in the Rrup calculation.</t>
-  </si>
-  <si>
-    <t>PART IV: Significant-duration measures</t>
+    <t>t_duration(NS)(D5_75)</t>
+  </si>
+  <si>
+    <t>Significant duration between 5% and 75% of Arias intensity for the NS component.</t>
   </si>
   <si>
     <t>AD</t>
   </si>
   <si>
-    <t>t_duration(EW)(D5_75)</t>
-  </si>
-  <si>
-    <t>Significant duration between 5% and 75% of Arias intensity for the EW component.</t>
-  </si>
-  <si>
-    <t>s</t>
-  </si>
-  <si>
-    <t>KiK-net surface acceleration record.</t>
-  </si>
-  <si>
-    <t>Calculated from the preprocessed component acceleration time history.</t>
-  </si>
-  <si>
-    <t>Computed separately for each component.</t>
+    <t>t_duration(UD)(D5_75)</t>
+  </si>
+  <si>
+    <t>Significant duration between 5% and 75% of Arias intensity for the UD component.</t>
   </si>
   <si>
     <t>AE</t>
   </si>
   <si>
-    <t>t_duration(NS)(D5_75)</t>
-  </si>
-  <si>
-    <t>Significant duration between 5% and 75% of Arias intensity for the NS component.</t>
+    <t>t_duration(EW)(D5_95)</t>
+  </si>
+  <si>
+    <t>Significant duration between 5% and 95% of Arias intensity for the EW component.</t>
   </si>
   <si>
     <t>AF</t>
   </si>
   <si>
-    <t>t_duration(UD)(D5_75)</t>
-  </si>
-  <si>
-    <t>Significant duration between 5% and 75% of Arias intensity for the UD component.</t>
+    <t>t_duration(NS)(D5_95)</t>
+  </si>
+  <si>
+    <t>Significant duration between 5% and 95% of Arias intensity for the NS component.</t>
   </si>
   <si>
     <t>AG</t>
   </si>
   <si>
-    <t>t_duration(EW)(D5_95)</t>
-  </si>
-  <si>
-    <t>Significant duration between 5% and 95% of Arias intensity for the EW component.</t>
+    <t>t_duration(UD)(D5_95)</t>
+  </si>
+  <si>
+    <t>Significant duration between 5% and 95% of Arias intensity for the UD component.</t>
+  </si>
+  <si>
+    <t>PART V: Intensity measures</t>
   </si>
   <si>
     <t>AH</t>
   </si>
   <si>
-    <t>t_duration(NS)(D5_95)</t>
-  </si>
-  <si>
-    <t>Significant duration between 5% and 95% of Arias intensity for the NS component.</t>
+    <t>PGA</t>
+  </si>
+  <si>
+    <t>Horizontal peak ground acceleration.</t>
+  </si>
+  <si>
+    <t>Gal (cm·s−2)</t>
+  </si>
+  <si>
+    <t>Geometric mean of PGA values calculated from the preprocessed EW and NS components.</t>
+  </si>
+  <si>
+    <t>The vertical component is not included in this published horizontal PGA field.</t>
   </si>
   <si>
     <t>AI</t>
   </si>
   <si>
-    <t>t_duration(UD)(D5_95)</t>
-  </si>
-  <si>
-    <t>Significant duration between 5% and 95% of Arias intensity for the UD component.</t>
-  </si>
-  <si>
-    <t>PART V: Intensity measures</t>
+    <t>PSA_0_050</t>
+  </si>
+  <si>
+    <t>5%-damped horizontal pseudo-spectral acceleration at oscillator period T = 0.05 s.</t>
+  </si>
+  <si>
+    <t>Geometric mean of PSA values calculated from the preprocessed EW and NS components.</t>
+  </si>
+  <si>
+    <t>T = 0.05 s</t>
   </si>
   <si>
     <t>AJ</t>
   </si>
   <si>
-    <t>PGA</t>
-  </si>
-  <si>
-    <t>Horizontal peak ground acceleration.</t>
-  </si>
-  <si>
-    <t>Gal (cm·s−2)</t>
-  </si>
-  <si>
-    <t>Geometric mean of PGA values calculated from the preprocessed EW and NS components.</t>
-  </si>
-  <si>
-    <t>The vertical component is not included in this published horizontal PGA field.</t>
+    <t>PSA_0_100</t>
+  </si>
+  <si>
+    <t>5%-damped horizontal pseudo-spectral acceleration at oscillator period T = 0.10 s.</t>
+  </si>
+  <si>
+    <t>T = 0.10 s</t>
   </si>
   <si>
     <t>AK</t>
   </si>
   <si>
-    <t>PSA_0_050</t>
-  </si>
-  <si>
-    <t>5%-damped horizontal pseudo-spectral acceleration at oscillator period T = 0.05 s.</t>
-  </si>
-  <si>
-    <t>Geometric mean of PSA values calculated from the preprocessed EW and NS components.</t>
-  </si>
-  <si>
-    <t>T = 0.05 s</t>
-  </si>
-  <si>
-    <t>Selected published ordinate from the response-spectrum calculation; the original calculation uses 500 logarithmically spaced periods from 0.05 to 20 s.</t>
+    <t>PSA_0_150</t>
+  </si>
+  <si>
+    <t>5%-damped horizontal pseudo-spectral acceleration at oscillator period T = 0.15 s.</t>
+  </si>
+  <si>
+    <t>T = 0.15 s</t>
   </si>
   <si>
     <t>AL</t>
   </si>
   <si>
-    <t>PSA_0_100</t>
-  </si>
-  <si>
-    <t>5%-damped horizontal pseudo-spectral acceleration at oscillator period T = 0.10 s.</t>
-  </si>
-  <si>
-    <t>T = 0.10 s</t>
+    <t>PSA_0_200</t>
+  </si>
+  <si>
+    <t>5%-damped horizontal pseudo-spectral acceleration at oscillator period T = 0.20 s.</t>
+  </si>
+  <si>
+    <t>T = 0.20 s</t>
   </si>
   <si>
     <t>AM</t>
   </si>
   <si>
-    <t>PSA_0_150</t>
-  </si>
-  <si>
-    <t>5%-damped horizontal pseudo-spectral acceleration at oscillator period T = 0.15 s.</t>
-  </si>
-  <si>
-    <t>T = 0.15 s</t>
+    <t>PSA_0_250</t>
+  </si>
+  <si>
+    <t>5%-damped horizontal pseudo-spectral acceleration at oscillator period T = 0.25 s.</t>
+  </si>
+  <si>
+    <t>T = 0.25 s</t>
   </si>
   <si>
     <t>AN</t>
   </si>
   <si>
-    <t>PSA_0_200</t>
-  </si>
-  <si>
-    <t>5%-damped horizontal pseudo-spectral acceleration at oscillator period T = 0.20 s.</t>
-  </si>
-  <si>
-    <t>T = 0.20 s</t>
+    <t>PSA_0_300</t>
+  </si>
+  <si>
+    <t>5%-damped horizontal pseudo-spectral acceleration at oscillator period T = 0.30 s.</t>
+  </si>
+  <si>
+    <t>T = 0.30 s</t>
   </si>
   <si>
     <t>AO</t>
   </si>
   <si>
-    <t>PSA_0_250</t>
-  </si>
-  <si>
-    <t>5%-damped horizontal pseudo-spectral acceleration at oscillator period T = 0.25 s.</t>
-  </si>
-  <si>
-    <t>T = 0.25 s</t>
+    <t>PSA_0_400</t>
+  </si>
+  <si>
+    <t>5%-damped horizontal pseudo-spectral acceleration at oscillator period T = 0.40 s.</t>
+  </si>
+  <si>
+    <t>T = 0.40 s</t>
   </si>
   <si>
     <t>AP</t>
   </si>
   <si>
-    <t>PSA_0_300</t>
-  </si>
-  <si>
-    <t>5%-damped horizontal pseudo-spectral acceleration at oscillator period T = 0.30 s.</t>
-  </si>
-  <si>
-    <t>T = 0.30 s</t>
+    <t>PSA_0_500</t>
+  </si>
+  <si>
+    <t>5%-damped horizontal pseudo-spectral acceleration at oscillator period T = 0.50 s.</t>
+  </si>
+  <si>
+    <t>T = 0.50 s</t>
   </si>
   <si>
     <t>AQ</t>
   </si>
   <si>
-    <t>PSA_0_400</t>
-  </si>
-  <si>
-    <t>5%-damped horizontal pseudo-spectral acceleration at oscillator period T = 0.40 s.</t>
-  </si>
-  <si>
-    <t>T = 0.40 s</t>
+    <t>PSA_0_600</t>
+  </si>
+  <si>
+    <t>5%-damped horizontal pseudo-spectral acceleration at oscillator period T = 0.60 s.</t>
+  </si>
+  <si>
+    <t>T = 0.60 s</t>
   </si>
   <si>
     <t>AR</t>
   </si>
   <si>
-    <t>PSA_0_500</t>
-  </si>
-  <si>
-    <t>5%-damped horizontal pseudo-spectral acceleration at oscillator period T = 0.50 s.</t>
-  </si>
-  <si>
-    <t>T = 0.50 s</t>
+    <t>PSA_0_700</t>
+  </si>
+  <si>
+    <t>5%-damped horizontal pseudo-spectral acceleration at oscillator period T = 0.70 s.</t>
+  </si>
+  <si>
+    <t>T = 0.70 s</t>
   </si>
   <si>
     <t>AS</t>
   </si>
   <si>
-    <t>PSA_0_600</t>
-  </si>
-  <si>
-    <t>5%-damped horizontal pseudo-spectral acceleration at oscillator period T = 0.60 s.</t>
-  </si>
-  <si>
-    <t>T = 0.60 s</t>
+    <t>PSA_0_800</t>
+  </si>
+  <si>
+    <t>5%-damped horizontal pseudo-spectral acceleration at oscillator period T = 0.80 s.</t>
+  </si>
+  <si>
+    <t>T = 0.80 s</t>
   </si>
   <si>
     <t>AT</t>
   </si>
   <si>
-    <t>PSA_0_700</t>
-  </si>
-  <si>
-    <t>5%-damped horizontal pseudo-spectral acceleration at oscillator period T = 0.70 s.</t>
-  </si>
-  <si>
-    <t>T = 0.70 s</t>
+    <t>PSA_0_900</t>
+  </si>
+  <si>
+    <t>5%-damped horizontal pseudo-spectral acceleration at oscillator period T = 0.90 s.</t>
+  </si>
+  <si>
+    <t>T = 0.90 s</t>
   </si>
   <si>
     <t>AU</t>
   </si>
   <si>
-    <t>PSA_0_800</t>
-  </si>
-  <si>
-    <t>5%-damped horizontal pseudo-spectral acceleration at oscillator period T = 0.80 s.</t>
-  </si>
-  <si>
-    <t>T = 0.80 s</t>
+    <t>PSA_1_000</t>
+  </si>
+  <si>
+    <t>5%-damped horizontal pseudo-spectral acceleration at oscillator period T = 1.00 s.</t>
+  </si>
+  <si>
+    <t>T = 1.00 s</t>
   </si>
   <si>
     <t>AV</t>
   </si>
   <si>
-    <t>PSA_0_900</t>
-  </si>
-  <si>
-    <t>5%-damped horizontal pseudo-spectral acceleration at oscillator period T = 0.90 s.</t>
-  </si>
-  <si>
-    <t>T = 0.90 s</t>
+    <t>PSA_1_250</t>
+  </si>
+  <si>
+    <t>5%-damped horizontal pseudo-spectral acceleration at oscillator period T = 1.25 s.</t>
+  </si>
+  <si>
+    <t>T = 1.25 s</t>
   </si>
   <si>
     <t>AW</t>
   </si>
   <si>
-    <t>PSA_1_000</t>
-  </si>
-  <si>
-    <t>5%-damped horizontal pseudo-spectral acceleration at oscillator period T = 1.00 s.</t>
-  </si>
-  <si>
-    <t>T = 1.00 s</t>
+    <t>PSA_1_500</t>
+  </si>
+  <si>
+    <t>5%-damped horizontal pseudo-spectral acceleration at oscillator period T = 1.50 s.</t>
+  </si>
+  <si>
+    <t>T = 1.50 s</t>
   </si>
   <si>
     <t>AX</t>
   </si>
   <si>
-    <t>PSA_1_250</t>
-  </si>
-  <si>
-    <t>5%-damped horizontal pseudo-spectral acceleration at oscillator period T = 1.25 s.</t>
-  </si>
-  <si>
-    <t>T = 1.25 s</t>
+    <t>PSA_2_000</t>
+  </si>
+  <si>
+    <t>5%-damped horizontal pseudo-spectral acceleration at oscillator period T = 2.00 s.</t>
+  </si>
+  <si>
+    <t>T = 2.00 s</t>
   </si>
   <si>
     <t>AY</t>
   </si>
   <si>
-    <t>PSA_1_500</t>
-  </si>
-  <si>
-    <t>5%-damped horizontal pseudo-spectral acceleration at oscillator period T = 1.50 s.</t>
-  </si>
-  <si>
-    <t>T = 1.50 s</t>
+    <t>PSA_2_500</t>
+  </si>
+  <si>
+    <t>5%-damped horizontal pseudo-spectral acceleration at oscillator period T = 2.50 s.</t>
+  </si>
+  <si>
+    <t>T = 2.50 s</t>
   </si>
   <si>
     <t>AZ</t>
   </si>
   <si>
-    <t>PSA_2_000</t>
-  </si>
-  <si>
-    <t>5%-damped horizontal pseudo-spectral acceleration at oscillator period T = 2.00 s.</t>
-  </si>
-  <si>
-    <t>T = 2.00 s</t>
+    <t>PSA_3_000</t>
+  </si>
+  <si>
+    <t>5%-damped horizontal pseudo-spectral acceleration at oscillator period T = 3.00 s.</t>
+  </si>
+  <si>
+    <t>T = 3.00 s</t>
   </si>
   <si>
     <t>BA</t>
   </si>
   <si>
-    <t>PSA_2_500</t>
-  </si>
-  <si>
-    <t>5%-damped horizontal pseudo-spectral acceleration at oscillator period T = 2.50 s.</t>
-  </si>
-  <si>
-    <t>T = 2.50 s</t>
+    <t>PSA_4_000</t>
+  </si>
+  <si>
+    <t>5%-damped horizontal pseudo-spectral acceleration at oscillator period T = 4.00 s.</t>
+  </si>
+  <si>
+    <t>T = 4.00 s</t>
   </si>
   <si>
     <t>BB</t>
   </si>
   <si>
-    <t>PSA_3_000</t>
-  </si>
-  <si>
-    <t>5%-damped horizontal pseudo-spectral acceleration at oscillator period T = 3.00 s.</t>
-  </si>
-  <si>
-    <t>T = 3.00 s</t>
-  </si>
-  <si>
-    <t>BC</t>
-  </si>
-  <si>
-    <t>PSA_4_000</t>
-  </si>
-  <si>
-    <t>5%-damped horizontal pseudo-spectral acceleration at oscillator period T = 4.00 s.</t>
-  </si>
-  <si>
-    <t>T = 4.00 s</t>
-  </si>
-  <si>
-    <t>BD</t>
-  </si>
-  <si>
     <t>PSA_5_000</t>
   </si>
   <si>
@@ -1119,39 +987,18 @@
     <t>Reverse/thrust mechanism</t>
   </si>
   <si>
-    <t>SS</t>
-  </si>
-  <si>
-    <t>Strike-slip faulting</t>
-  </si>
-  <si>
-    <t>Independent faulting-style metadata</t>
+    <t>A unique classification could not be obtained or valid P- or T-axis parameters were unavailable</t>
+  </si>
+  <si>
+    <t>Non-frozen state</t>
+  </si>
+  <si>
+    <t>Event-date environmental annotation</t>
   </si>
   <si>
     <t>Not used</t>
   </si>
   <si>
-    <t>NF</t>
-  </si>
-  <si>
-    <t>Normal faulting</t>
-  </si>
-  <si>
-    <t>TF</t>
-  </si>
-  <si>
-    <t>Thrust/reverse faulting</t>
-  </si>
-  <si>
-    <t>Indeterminate event-scale faulting type</t>
-  </si>
-  <si>
-    <t>Non-frozen state</t>
-  </si>
-  <si>
-    <t>Event-date environmental annotation</t>
-  </si>
-  <si>
     <t>Frozen state</t>
   </si>
   <si>
@@ -1164,58 +1011,31 @@
     <t>Site-condition metadata</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2937"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>Not used in R</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="subscript"/>
-        <sz val="10"/>
-        <color rgb="FF1F2937"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>rup</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2937"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> construction</t>
-    </r>
+    <t>Not used in Rrup construction</t>
   </si>
   <si>
     <t>SCI</t>
   </si>
   <si>
-    <t>Japanese Vs30-based site class I</t>
+    <t>Japanese site class I</t>
   </si>
   <si>
     <t>SCII</t>
   </si>
   <si>
-    <t>Japanese Vs30-based site class II</t>
+    <t>Japanese site class II</t>
   </si>
   <si>
     <t>SCIII</t>
   </si>
   <si>
-    <t>Japanese Vs30-based site class III</t>
+    <t>Japanese site class III</t>
   </si>
   <si>
     <t>SCIV</t>
   </si>
   <si>
-    <t>Japanese Vs30-based site class IV</t>
+    <t>Japanese site class IV</t>
   </si>
   <si>
     <t>Current rupture-distance workflow</t>
@@ -1245,7 +1065,7 @@
     <t>Used in Zhao-type tectonic classification</t>
   </si>
   <si>
-    <t>TOF(P-T axes), focal depth, source position relative to the slab interface, slab-interface dip, and F-net nodal-plane dip</t>
+    <t>TOF(P-T axes), focal depth, source position relative to the slab interface, slab-interface dip, and dip of the identified rupture plane from the F-net focal-mechanism solution</t>
   </si>
   <si>
     <t>Apply Zhao-type classification</t>
@@ -1255,27 +1075,6 @@
   </si>
   <si>
     <t>Use the public finite-fault rupture surface where available</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2937"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>R</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="subscript"/>
-        <sz val="10"/>
-        <color rgb="FF1F2937"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>rup</t>
-    </r>
   </si>
   <si>
     <t>First-priority rupture representation</t>
@@ -1312,7 +1111,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -1375,30 +1174,24 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -1406,15 +1199,13 @@
       <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
       <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -1422,7 +1213,6 @@
       <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -1430,7 +1220,6 @@
       <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -1438,106 +1227,73 @@
       <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <vertAlign val="subscript"/>
-      <sz val="10"/>
-      <color rgb="FF17365D"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <vertAlign val="subscript"/>
-      <sz val="10"/>
-      <color rgb="FF1F2937"/>
-      <name val="Arial"/>
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="43">
+  <fills count="42">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1576,8 +1332,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.79998"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
@@ -1654,19 +1410,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.59999"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1678,19 +1428,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.79998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.59999"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1702,19 +1452,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.79998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.59999"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1726,19 +1476,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.79998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.59999"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1750,19 +1500,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.79998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.59999"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1774,24 +1524,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.79998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.59999"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="21">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -1859,28 +1609,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFC8D4DF"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FFC8D4DF"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFC8D4DF"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FFC8D4DF"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color auto="1"/>
       </left>
       <right style="thin">
@@ -1889,43 +1617,6 @@
       <top style="thin">
         <color auto="1"/>
       </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
@@ -1960,7 +1651,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4" tint="0.49998"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2055,7 +1746,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="13" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2067,34 +1758,34 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2109,78 +1800,78 @@
     <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2215,79 +1906,49 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="7" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="7" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="7" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="7" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="7" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="9" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="7" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="9" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="7" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="9" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="10" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="11" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="12" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="10" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="11" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="12" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="10" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="11" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="12" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="10" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="11" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="12" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2609,9 +2270,9 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -2715,8 +2376,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K100"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <dimension ref="A1:K99"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
@@ -2732,966 +2393,946 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:11">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="12"/>
+      <c r="J1" s="12"/>
+      <c r="K1" s="12"/>
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:11">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15"/>
-      <c r="J2" s="15"/>
-      <c r="K2" s="15"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
+      <c r="K2" s="13"/>
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:11">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="16"/>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="16"/>
-      <c r="H3" s="16"/>
-      <c r="I3" s="16"/>
-      <c r="J3" s="16"/>
-      <c r="K3" s="16"/>
+      <c r="B3" s="14"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="14"/>
+      <c r="K3" s="14"/>
     </row>
     <row r="4" spans="1:11">
-      <c r="A4" s="17"/>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
-      <c r="H4" s="17"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="17"/>
+      <c r="A4" s="15"/>
+      <c r="B4" s="15"/>
+      <c r="C4" s="15"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="15"/>
+      <c r="G4" s="15"/>
+      <c r="H4" s="15"/>
+      <c r="I4" s="15"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="15"/>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:11">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="18" t="s">
+      <c r="C5" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="18" t="s">
+      <c r="D5" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="18" t="s">
+      <c r="E5" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="18" t="s">
+      <c r="F5" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="18" t="s">
+      <c r="G5" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="H5" s="18" t="s">
+      <c r="H5" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="I5" s="18" t="s">
+      <c r="I5" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="J5" s="18" t="s">
+      <c r="J5" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="K5" s="18" t="s">
+      <c r="K5" s="16" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:11">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="20" t="s">
+      <c r="B6" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="20" t="s">
+      <c r="C6" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="21" t="s">
+      <c r="D6" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="21" t="s">
+      <c r="E6" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="F6" s="21" t="s">
+      <c r="F6" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="G6" s="21" t="s">
+      <c r="G6" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="H6" s="21" t="s">
+      <c r="H6" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="I6" s="21" t="s">
+      <c r="I6" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="J6" s="21" t="s">
+      <c r="J6" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="K6" s="21" t="s">
+      <c r="K6" s="19" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:11">
-      <c r="A7" s="19"/>
-      <c r="B7" s="22" t="s">
+      <c r="A7" s="17"/>
+      <c r="B7" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="22" t="s">
+      <c r="C7" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="23" t="s">
+      <c r="D7" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="E7" s="23" t="s">
+      <c r="E7" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="F7" s="23" t="s">
+      <c r="F7" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="G7" s="23" t="s">
+      <c r="G7" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="H7" s="23" t="s">
+      <c r="H7" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="I7" s="23" t="s">
+      <c r="I7" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="J7" s="23" t="s">
+      <c r="J7" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="K7" s="23" t="s">
+      <c r="K7" s="21" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:11">
-      <c r="A8" s="19"/>
-      <c r="B8" s="20" t="s">
+      <c r="A8" s="17"/>
+      <c r="B8" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="C8" s="20" t="s">
+      <c r="C8" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="D8" s="21" t="s">
+      <c r="D8" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="E8" s="21" t="s">
+      <c r="E8" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="F8" s="21" t="s">
+      <c r="F8" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="G8" s="21" t="s">
+      <c r="G8" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="H8" s="21" t="s">
+      <c r="H8" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="I8" s="21" t="s">
+      <c r="I8" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="J8" s="21" t="s">
+      <c r="J8" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="K8" s="21"/>
+      <c r="K8" s="19"/>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:11">
-      <c r="A9" s="19"/>
-      <c r="B9" s="22" t="s">
+      <c r="A9" s="17"/>
+      <c r="B9" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="C9" s="22" t="s">
+      <c r="C9" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="D9" s="23" t="s">
+      <c r="D9" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="E9" s="23" t="s">
+      <c r="E9" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="F9" s="23" t="s">
+      <c r="F9" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="G9" s="23" t="s">
+      <c r="G9" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="H9" s="23" t="s">
+      <c r="H9" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="I9" s="23" t="s">
+      <c r="I9" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="J9" s="23" t="s">
+      <c r="J9" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="23"/>
+      <c r="K9" s="21"/>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:11">
-      <c r="A10" s="19"/>
-      <c r="B10" s="20" t="s">
+      <c r="A10" s="17"/>
+      <c r="B10" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="C10" s="20" t="s">
+      <c r="C10" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="D10" s="21" t="s">
+      <c r="D10" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="E10" s="21" t="s">
+      <c r="E10" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="F10" s="21" t="s">
+      <c r="F10" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="G10" s="21" t="s">
+      <c r="G10" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="H10" s="21" t="s">
+      <c r="H10" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="I10" s="21" t="s">
+      <c r="I10" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="J10" s="21" t="s">
+      <c r="J10" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="K10" s="21"/>
+      <c r="K10" s="19"/>
     </row>
     <row r="11" ht="36" customHeight="1" spans="1:11">
-      <c r="A11" s="19"/>
-      <c r="B11" s="22" t="s">
+      <c r="A11" s="17"/>
+      <c r="B11" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="C11" s="22" t="s">
+      <c r="C11" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="D11" s="23" t="s">
+      <c r="D11" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="E11" s="23" t="s">
+      <c r="E11" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="F11" s="23" t="s">
+      <c r="F11" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="G11" s="23" t="s">
+      <c r="G11" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="H11" s="23" t="s">
+      <c r="H11" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="I11" s="23" t="s">
+      <c r="I11" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="J11" s="23" t="s">
+      <c r="J11" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="K11" s="23" t="s">
+      <c r="K11" s="21" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:11">
-      <c r="A12" s="19"/>
-      <c r="B12" s="20" t="s">
+      <c r="A12" s="17"/>
+      <c r="B12" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="C12" s="20" t="s">
+      <c r="C12" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="D12" s="21" t="s">
+      <c r="D12" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="E12" s="21" t="s">
+      <c r="E12" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="F12" s="21" t="s">
+      <c r="F12" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="G12" s="21" t="s">
+      <c r="G12" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="H12" s="21" t="s">
+      <c r="H12" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="I12" s="21" t="s">
+      <c r="I12" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="J12" s="21" t="s">
+      <c r="J12" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="K12" s="21" t="s">
+      <c r="K12" s="19" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:11">
-      <c r="A13" s="19"/>
-      <c r="B13" s="22" t="s">
+      <c r="A13" s="17"/>
+      <c r="B13" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="C13" s="22" t="s">
+      <c r="C13" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="D13" s="23" t="s">
+      <c r="D13" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="E13" s="23" t="s">
+      <c r="E13" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="F13" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="G13" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="H13" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="I13" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="J13" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="K13" s="21"/>
+    </row>
+    <row r="14" ht="24" customHeight="1" spans="1:11">
+      <c r="A14" s="17"/>
+      <c r="B14" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="D14" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="E14" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="F14" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="G14" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="H14" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="I14" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="J14" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="K14" s="19"/>
+    </row>
+    <row r="15" ht="24" customHeight="1" spans="1:11">
+      <c r="A15" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="B15" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="C15" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="D15" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="E15" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="F13" s="23" t="s">
+      <c r="F15" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="G13" s="23" t="s">
-        <v>66</v>
-      </c>
-      <c r="H13" s="23" t="s">
-        <v>67</v>
-      </c>
-      <c r="I13" s="23" t="s">
-        <v>68</v>
-      </c>
-      <c r="J13" s="23" t="s">
+      <c r="G15" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="H15" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="I15" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="J15" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="K13" s="23" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="14" ht="24" customHeight="1" spans="1:11">
-      <c r="A14" s="19"/>
-      <c r="B14" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="C14" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="D14" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="E14" s="21" t="s">
+      <c r="K15" s="26"/>
+    </row>
+    <row r="16" ht="24" customHeight="1" spans="1:11">
+      <c r="A16" s="22"/>
+      <c r="B16" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="C16" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="D16" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="E16" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="F14" s="21" t="s">
+      <c r="F16" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G16" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="H16" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="I16" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="J16" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="K16" s="19"/>
+    </row>
+    <row r="17" ht="24" customHeight="1" spans="1:11">
+      <c r="A17" s="22"/>
+      <c r="B17" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="C17" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="D17" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="E17" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="F17" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="G17" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="H17" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="I17" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="J17" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="K17" s="21"/>
+    </row>
+    <row r="18" ht="24" customHeight="1" spans="1:11">
+      <c r="A18" s="22"/>
+      <c r="B18" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="C18" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="D18" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="E18" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="F18" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G18" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="H18" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="I18" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="J18" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="K18" s="19"/>
+    </row>
+    <row r="19" ht="24" customHeight="1" spans="1:11">
+      <c r="A19" s="22"/>
+      <c r="B19" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="C19" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="D19" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="E19" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="F19" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="G19" s="21" t="s">
+        <v>91</v>
+      </c>
+      <c r="H19" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="I19" s="21" t="s">
+        <v>97</v>
+      </c>
+      <c r="J19" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="K19" s="21"/>
+    </row>
+    <row r="20" ht="24" customHeight="1" spans="1:11">
+      <c r="A20" s="22"/>
+      <c r="B20" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="C20" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="D20" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="E20" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="F20" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="G14" s="21" t="s">
-        <v>73</v>
-      </c>
-      <c r="H14" s="21" t="s">
-        <v>38</v>
-      </c>
-      <c r="I14" s="21" t="s">
-        <v>74</v>
-      </c>
-      <c r="J14" s="21" t="s">
+      <c r="G20" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="H20" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="I20" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="J20" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="K14" s="21" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="15" ht="24" customHeight="1" spans="1:11">
-      <c r="A15" s="19"/>
-      <c r="B15" s="22" t="s">
-        <v>76</v>
-      </c>
-      <c r="C15" s="22" t="s">
-        <v>77</v>
-      </c>
-      <c r="D15" s="23" t="s">
+      <c r="K20" s="19"/>
+    </row>
+    <row r="21" ht="24" customHeight="1" spans="1:11">
+      <c r="A21" s="22"/>
+      <c r="B21" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="C21" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="D21" s="21" t="s">
+        <v>103</v>
+      </c>
+      <c r="E21" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="F21" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="G21" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="H21" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="E15" s="23" t="s">
+      <c r="I21" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="J21" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="F15" s="23" t="s">
+      <c r="K21" s="21"/>
+    </row>
+    <row r="22" ht="24" customHeight="1" spans="1:11">
+      <c r="A22" s="22"/>
+      <c r="B22" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="C22" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="D22" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="E22" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="F22" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="G15" s="23" t="s">
-        <v>79</v>
-      </c>
-      <c r="H15" s="23" t="s">
-        <v>38</v>
-      </c>
-      <c r="I15" s="23" t="s">
-        <v>80</v>
-      </c>
-      <c r="J15" s="23" t="s">
+      <c r="G22" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="H22" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="I22" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="J22" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="K15" s="36" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="16" ht="24" customHeight="1" spans="1:11">
-      <c r="A16" s="24" t="s">
-        <v>81</v>
-      </c>
-      <c r="B16" s="20" t="s">
-        <v>82</v>
-      </c>
-      <c r="C16" s="20" t="s">
-        <v>83</v>
-      </c>
-      <c r="D16" s="21" t="s">
-        <v>84</v>
-      </c>
-      <c r="E16" s="21" t="s">
-        <v>51</v>
-      </c>
-      <c r="F16" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="G16" s="21" t="s">
-        <v>85</v>
-      </c>
-      <c r="H16" s="21" t="s">
-        <v>86</v>
-      </c>
-      <c r="I16" s="21" t="s">
-        <v>87</v>
-      </c>
-      <c r="J16" s="21" t="s">
+      <c r="K22" s="19" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="23" ht="24" customHeight="1" spans="1:11">
+      <c r="A23" s="22"/>
+      <c r="B23" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="C23" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="D23" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="E23" s="21" t="s">
+        <v>114</v>
+      </c>
+      <c r="F23" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="G23" s="21" t="s">
+        <v>115</v>
+      </c>
+      <c r="H23" s="21" t="s">
+        <v>116</v>
+      </c>
+      <c r="I23" s="21" t="s">
+        <v>117</v>
+      </c>
+      <c r="J23" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="K16" s="21" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="17" ht="24" customHeight="1" spans="1:11">
-      <c r="A17" s="25"/>
-      <c r="B17" s="22" t="s">
-        <v>88</v>
-      </c>
-      <c r="C17" s="22" t="s">
-        <v>89</v>
-      </c>
-      <c r="D17" s="23" t="s">
-        <v>90</v>
-      </c>
-      <c r="E17" s="23" t="s">
+      <c r="K23" s="21" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="24" ht="24" customHeight="1" spans="1:11">
+      <c r="A24" s="22"/>
+      <c r="B24" s="18" t="s">
+        <v>119</v>
+      </c>
+      <c r="C24" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="D24" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="E24" s="19" t="s">
+        <v>122</v>
+      </c>
+      <c r="F24" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="G24" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="H24" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="I24" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="J24" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="F17" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="G17" s="23" t="s">
-        <v>91</v>
-      </c>
-      <c r="H17" s="23" t="s">
-        <v>86</v>
-      </c>
-      <c r="I17" s="23" t="s">
-        <v>92</v>
-      </c>
-      <c r="J17" s="23" t="s">
+      <c r="K24" s="19" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="25" ht="24" customHeight="1" spans="1:11">
+      <c r="A25" s="22"/>
+      <c r="B25" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="C25" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="D25" s="21" t="s">
+        <v>129</v>
+      </c>
+      <c r="E25" s="21" t="s">
+        <v>130</v>
+      </c>
+      <c r="F25" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="G25" s="21" t="s">
+        <v>131</v>
+      </c>
+      <c r="H25" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="I25" s="21" t="s">
+        <v>117</v>
+      </c>
+      <c r="J25" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="K17" s="23" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="18" ht="24" customHeight="1" spans="1:11">
-      <c r="A18" s="25"/>
-      <c r="B18" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="C18" s="20" t="s">
-        <v>93</v>
-      </c>
-      <c r="D18" s="21" t="s">
-        <v>94</v>
-      </c>
-      <c r="E18" s="21" t="s">
+      <c r="K25" s="21" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="26" ht="24" customHeight="1" spans="1:11">
+      <c r="A26" s="22"/>
+      <c r="B26" s="18" t="s">
+        <v>134</v>
+      </c>
+      <c r="C26" s="18" t="s">
+        <v>135</v>
+      </c>
+      <c r="D26" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="E26" s="19" t="s">
+        <v>137</v>
+      </c>
+      <c r="F26" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="G26" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="H26" s="19" t="s">
+        <v>139</v>
+      </c>
+      <c r="I26" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="J26" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="F18" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="G18" s="21" t="s">
-        <v>91</v>
-      </c>
-      <c r="H18" s="21" t="s">
-        <v>86</v>
-      </c>
-      <c r="I18" s="21" t="s">
-        <v>95</v>
-      </c>
-      <c r="J18" s="21" t="s">
+      <c r="K26" s="19" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="27" ht="24" customHeight="1" spans="1:11">
+      <c r="A27" s="22"/>
+      <c r="B27" s="20" t="s">
+        <v>142</v>
+      </c>
+      <c r="C27" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="D27" s="21" t="s">
+        <v>144</v>
+      </c>
+      <c r="E27" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="F27" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="G27" s="21" t="s">
+        <v>145</v>
+      </c>
+      <c r="H27" s="21" t="s">
+        <v>146</v>
+      </c>
+      <c r="I27" s="21" t="s">
+        <v>147</v>
+      </c>
+      <c r="J27" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="K18" s="21" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="19" ht="24" customHeight="1" spans="1:11">
-      <c r="A19" s="25"/>
-      <c r="B19" s="22" t="s">
-        <v>96</v>
-      </c>
-      <c r="C19" s="22" t="s">
-        <v>97</v>
-      </c>
-      <c r="D19" s="23" t="s">
-        <v>98</v>
-      </c>
-      <c r="E19" s="23" t="s">
-        <v>18</v>
-      </c>
-      <c r="F19" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="G19" s="23" t="s">
-        <v>99</v>
-      </c>
-      <c r="H19" s="23" t="s">
-        <v>100</v>
-      </c>
-      <c r="I19" s="23" t="s">
-        <v>101</v>
-      </c>
-      <c r="J19" s="23" t="s">
-        <v>18</v>
-      </c>
-      <c r="K19" s="23" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="20" ht="24" customHeight="1" spans="1:11">
-      <c r="A20" s="25"/>
-      <c r="B20" s="20" t="s">
-        <v>102</v>
-      </c>
-      <c r="C20" s="20" t="s">
-        <v>103</v>
-      </c>
-      <c r="D20" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="E20" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="F20" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="G20" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="H20" s="21" t="s">
-        <v>100</v>
-      </c>
-      <c r="I20" s="21" t="s">
-        <v>105</v>
-      </c>
-      <c r="J20" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="K20" s="21" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="21" ht="24" customHeight="1" spans="1:11">
-      <c r="A21" s="25"/>
-      <c r="B21" s="22" t="s">
-        <v>106</v>
-      </c>
-      <c r="C21" s="22" t="s">
-        <v>107</v>
-      </c>
-      <c r="D21" s="23" t="s">
-        <v>108</v>
-      </c>
-      <c r="E21" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="F21" s="23" t="s">
-        <v>37</v>
-      </c>
-      <c r="G21" s="23" t="s">
-        <v>91</v>
-      </c>
-      <c r="H21" s="23" t="s">
-        <v>86</v>
-      </c>
-      <c r="I21" s="23" t="s">
-        <v>39</v>
-      </c>
-      <c r="J21" s="23" t="s">
-        <v>18</v>
-      </c>
-      <c r="K21" s="23" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="22" ht="24" customHeight="1" spans="1:11">
-      <c r="A22" s="25"/>
-      <c r="B22" s="20" t="s">
-        <v>109</v>
-      </c>
-      <c r="C22" s="20" t="s">
-        <v>110</v>
-      </c>
-      <c r="D22" s="21" t="s">
-        <v>111</v>
-      </c>
-      <c r="E22" s="21" t="s">
-        <v>36</v>
-      </c>
-      <c r="F22" s="21" t="s">
-        <v>37</v>
-      </c>
-      <c r="G22" s="21" t="s">
-        <v>91</v>
-      </c>
-      <c r="H22" s="21" t="s">
-        <v>86</v>
-      </c>
-      <c r="I22" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="J22" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="K22" s="21" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="23" ht="24" customHeight="1" spans="1:11">
-      <c r="A23" s="25"/>
-      <c r="B23" s="22" t="s">
-        <v>112</v>
-      </c>
-      <c r="C23" s="22" t="s">
-        <v>113</v>
-      </c>
-      <c r="D23" s="23" t="s">
-        <v>114</v>
-      </c>
-      <c r="E23" s="23" t="s">
-        <v>115</v>
-      </c>
-      <c r="F23" s="23" t="s">
-        <v>37</v>
-      </c>
-      <c r="G23" s="23" t="s">
-        <v>116</v>
-      </c>
-      <c r="H23" s="23" t="s">
-        <v>117</v>
-      </c>
-      <c r="I23" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="J23" s="23" t="s">
-        <v>18</v>
-      </c>
-      <c r="K23" s="23" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="24" ht="24" customHeight="1" spans="1:11">
-      <c r="A24" s="25"/>
-      <c r="B24" s="20" t="s">
-        <v>119</v>
-      </c>
-      <c r="C24" s="20" t="s">
-        <v>120</v>
-      </c>
-      <c r="D24" s="21" t="s">
-        <v>121</v>
-      </c>
-      <c r="E24" s="21" t="s">
-        <v>122</v>
-      </c>
-      <c r="F24" s="21" t="s">
-        <v>37</v>
-      </c>
-      <c r="G24" s="21" t="s">
-        <v>123</v>
-      </c>
-      <c r="H24" s="21" t="s">
-        <v>124</v>
-      </c>
-      <c r="I24" s="21" t="s">
-        <v>125</v>
-      </c>
-      <c r="J24" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="K24" s="21" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="25" ht="24" customHeight="1" spans="1:11">
-      <c r="A25" s="25"/>
-      <c r="B25" s="22" t="s">
-        <v>127</v>
-      </c>
-      <c r="C25" s="22" t="s">
-        <v>128</v>
-      </c>
-      <c r="D25" s="23" t="s">
-        <v>129</v>
-      </c>
-      <c r="E25" s="23" t="s">
-        <v>130</v>
-      </c>
-      <c r="F25" s="23" t="s">
-        <v>37</v>
-      </c>
-      <c r="G25" s="23" t="s">
-        <v>131</v>
-      </c>
-      <c r="H25" s="23" t="s">
-        <v>132</v>
-      </c>
-      <c r="I25" s="23" t="s">
-        <v>133</v>
-      </c>
-      <c r="J25" s="23" t="s">
-        <v>18</v>
-      </c>
-      <c r="K25" s="23" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="26" ht="24" customHeight="1" spans="1:11">
-      <c r="A26" s="25"/>
-      <c r="B26" s="20" t="s">
-        <v>135</v>
-      </c>
-      <c r="C26" s="20" t="s">
-        <v>136</v>
-      </c>
-      <c r="D26" s="21" t="s">
-        <v>137</v>
-      </c>
-      <c r="E26" s="21" t="s">
-        <v>138</v>
-      </c>
-      <c r="F26" s="21" t="s">
-        <v>37</v>
-      </c>
-      <c r="G26" s="21" t="s">
-        <v>139</v>
-      </c>
-      <c r="H26" s="21" t="s">
-        <v>140</v>
-      </c>
-      <c r="I26" s="21" t="s">
-        <v>125</v>
-      </c>
-      <c r="J26" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="K26" s="21" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="27" ht="24" customHeight="1" spans="1:11">
-      <c r="A27" s="25"/>
-      <c r="B27" s="22" t="s">
-        <v>142</v>
-      </c>
-      <c r="C27" s="22" t="s">
-        <v>143</v>
-      </c>
-      <c r="D27" s="23" t="s">
-        <v>144</v>
-      </c>
-      <c r="E27" s="23" t="s">
-        <v>145</v>
-      </c>
-      <c r="F27" s="23" t="s">
-        <v>146</v>
-      </c>
-      <c r="G27" s="23" t="s">
-        <v>123</v>
-      </c>
-      <c r="H27" s="23" t="s">
-        <v>147</v>
-      </c>
-      <c r="I27" s="23" t="s">
+      <c r="K27" s="21" t="s">
         <v>148</v>
       </c>
-      <c r="J27" s="23" t="s">
-        <v>18</v>
-      </c>
-      <c r="K27" s="23" t="s">
+    </row>
+    <row r="28" ht="24" customHeight="1" spans="1:11">
+      <c r="A28" s="22"/>
+      <c r="B28" s="20" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="28" ht="24" customHeight="1" spans="1:11">
-      <c r="A28" s="25"/>
-      <c r="B28" s="20" t="s">
+      <c r="C28" s="20" t="s">
         <v>150</v>
       </c>
-      <c r="C28" s="20" t="s">
+      <c r="D28" s="21" t="s">
         <v>151</v>
       </c>
-      <c r="D28" s="21" t="s">
+      <c r="E28" s="21" t="s">
         <v>152</v>
-      </c>
-      <c r="E28" s="21" t="s">
-        <v>153</v>
       </c>
       <c r="F28" s="21" t="s">
         <v>37</v>
       </c>
       <c r="G28" s="21" t="s">
-        <v>123</v>
+        <v>153</v>
       </c>
       <c r="H28" s="21" t="s">
         <v>154</v>
       </c>
       <c r="I28" s="21" t="s">
-        <v>125</v>
+        <v>155</v>
       </c>
       <c r="J28" s="21" t="s">
         <v>18</v>
       </c>
       <c r="K28" s="21" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="29" ht="24" customHeight="1" spans="1:11">
-      <c r="A29" s="25"/>
-      <c r="B29" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="C29" s="22" t="s">
+      <c r="A29" s="22"/>
+      <c r="B29" s="20" t="s">
         <v>157</v>
       </c>
-      <c r="D29" s="23" t="s">
+      <c r="C29" s="18" t="s">
         <v>158</v>
       </c>
-      <c r="E29" s="23" t="s">
+      <c r="D29" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="E29" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="F29" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G29" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="H29" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="I29" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="J29" s="19">
+        <v>-999</v>
+      </c>
+      <c r="K29" s="19" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="30" ht="24" customHeight="1" spans="1:11">
+      <c r="A30" s="22" t="s">
+        <v>164</v>
+      </c>
+      <c r="B30" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="C30" s="20" t="s">
+        <v>166</v>
+      </c>
+      <c r="D30" s="21" t="s">
+        <v>167</v>
+      </c>
+      <c r="E30" s="21" t="s">
         <v>46</v>
-      </c>
-      <c r="F29" s="23" t="s">
-        <v>37</v>
-      </c>
-      <c r="G29" s="23" t="s">
-        <v>159</v>
-      </c>
-      <c r="H29" s="23" t="s">
-        <v>160</v>
-      </c>
-      <c r="I29" s="23" t="s">
-        <v>161</v>
-      </c>
-      <c r="J29" s="23" t="s">
-        <v>18</v>
-      </c>
-      <c r="K29" s="23" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="30" ht="24" customHeight="1" spans="1:11">
-      <c r="A30" s="25"/>
-      <c r="B30" s="20" t="s">
-        <v>163</v>
-      </c>
-      <c r="C30" s="20" t="s">
-        <v>164</v>
-      </c>
-      <c r="D30" s="21" t="s">
-        <v>165</v>
-      </c>
-      <c r="E30" s="21" t="s">
-        <v>166</v>
       </c>
       <c r="F30" s="21" t="s">
         <v>37</v>
       </c>
       <c r="G30" s="21" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H30" s="21" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I30" s="21" t="s">
-        <v>169</v>
+        <v>117</v>
       </c>
       <c r="J30" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="K30" s="21" t="s">
+      <c r="K30" s="21"/>
+    </row>
+    <row r="31" ht="24" customHeight="1" spans="1:11">
+      <c r="A31" s="23"/>
+      <c r="B31" s="20" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="31" ht="24" customHeight="1" spans="1:11">
-      <c r="A31" s="26"/>
-      <c r="B31" s="22" t="s">
+      <c r="C31" s="18" t="s">
         <v>171</v>
       </c>
-      <c r="C31" s="22" t="s">
+      <c r="D31" s="19" t="s">
         <v>172</v>
       </c>
-      <c r="D31" s="23" t="s">
+      <c r="E31" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="F31" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="G31" s="19" t="s">
         <v>173</v>
       </c>
-      <c r="E31" s="23" t="s">
-        <v>51</v>
-      </c>
-      <c r="F31" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="G31" s="23" t="s">
+      <c r="H31" s="19" t="s">
         <v>174</v>
       </c>
-      <c r="H31" s="23" t="s">
+      <c r="I31" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="J31" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="K31" s="19" t="s">
         <v>175</v>
       </c>
-      <c r="I31" s="23" t="s">
+    </row>
+    <row r="32" ht="24" customHeight="1" spans="1:11">
+      <c r="A32" s="23"/>
+      <c r="B32" s="18" t="s">
         <v>176</v>
       </c>
-      <c r="J31" s="23">
-        <v>-999</v>
-      </c>
-      <c r="K31" s="23" t="s">
+      <c r="C32" s="20" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="32" ht="24" customHeight="1" spans="1:11">
-      <c r="A32" s="27" t="s">
+      <c r="D32" s="21" t="s">
         <v>178</v>
-      </c>
-      <c r="B32" s="20" t="s">
-        <v>179</v>
-      </c>
-      <c r="C32" s="20" t="s">
-        <v>180</v>
-      </c>
-      <c r="D32" s="21" t="s">
-        <v>181</v>
       </c>
       <c r="E32" s="21" t="s">
         <v>46</v>
@@ -3700,1499 +3341,1397 @@
         <v>37</v>
       </c>
       <c r="G32" s="21" t="s">
+        <v>179</v>
+      </c>
+      <c r="H32" s="21" t="s">
+        <v>180</v>
+      </c>
+      <c r="I32" s="21" t="s">
+        <v>181</v>
+      </c>
+      <c r="J32" s="21">
+        <v>-999</v>
+      </c>
+      <c r="K32" s="21" t="s">
         <v>182</v>
       </c>
-      <c r="H32" s="21" t="s">
+    </row>
+    <row r="33" ht="72" customHeight="1" spans="1:11">
+      <c r="A33" s="23" t="s">
         <v>183</v>
       </c>
-      <c r="I32" s="21" t="s">
-        <v>125</v>
-      </c>
-      <c r="J32" s="21" t="s">
+      <c r="B33" s="20" t="s">
+        <v>184</v>
+      </c>
+      <c r="C33" s="18" t="s">
+        <v>185</v>
+      </c>
+      <c r="D33" s="19" t="s">
+        <v>186</v>
+      </c>
+      <c r="E33" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="F33" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="G33" s="19" t="s">
+        <v>188</v>
+      </c>
+      <c r="H33" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="I33" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="J33" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="K32" s="21" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="33" ht="24" customHeight="1" spans="1:11">
-      <c r="A33" s="28"/>
-      <c r="B33" s="22" t="s">
-        <v>184</v>
-      </c>
-      <c r="C33" s="22" t="s">
-        <v>185</v>
-      </c>
-      <c r="D33" s="23" t="s">
-        <v>186</v>
-      </c>
-      <c r="E33" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="F33" s="23" t="s">
-        <v>37</v>
-      </c>
-      <c r="G33" s="23" t="s">
+      <c r="K33" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="34" ht="24" customHeight="1" spans="1:11">
+      <c r="A34" s="24"/>
+      <c r="B34" s="18" t="s">
+        <v>191</v>
+      </c>
+      <c r="C34" s="20" t="s">
+        <v>192</v>
+      </c>
+      <c r="D34" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="E34" s="21" t="s">
         <v>187</v>
-      </c>
-      <c r="H33" s="23" t="s">
-        <v>188</v>
-      </c>
-      <c r="I33" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="J33" s="23" t="s">
-        <v>18</v>
-      </c>
-      <c r="K33" s="23" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="34" ht="72" customHeight="1" spans="1:11">
-      <c r="A34" s="29"/>
-      <c r="B34" s="20" t="s">
-        <v>190</v>
-      </c>
-      <c r="C34" s="20" t="s">
-        <v>191</v>
-      </c>
-      <c r="D34" s="21" t="s">
-        <v>192</v>
-      </c>
-      <c r="E34" s="21" t="s">
-        <v>46</v>
       </c>
       <c r="F34" s="21" t="s">
         <v>37</v>
       </c>
       <c r="G34" s="21" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="H34" s="21" t="s">
+        <v>189</v>
+      </c>
+      <c r="I34" s="21" t="s">
+        <v>117</v>
+      </c>
+      <c r="J34" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="K34" s="21" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="35" ht="24" customHeight="1" spans="1:11">
+      <c r="A35" s="24"/>
+      <c r="B35" s="20" t="s">
         <v>194</v>
       </c>
-      <c r="I34" s="21" t="s">
+      <c r="C35" s="18" t="s">
         <v>195</v>
       </c>
-      <c r="J34" s="21">
-        <v>-999</v>
-      </c>
-      <c r="K34" s="21" t="s">
+      <c r="D35" s="19" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="35" ht="24" customHeight="1" spans="1:11">
-      <c r="A35" s="30" t="s">
+      <c r="E35" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="F35" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="G35" s="19" t="s">
+        <v>188</v>
+      </c>
+      <c r="H35" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="I35" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="J35" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="K35" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="36" ht="24" customHeight="1" spans="1:11">
+      <c r="A36" s="24"/>
+      <c r="B36" s="18" t="s">
         <v>197</v>
       </c>
-      <c r="B35" s="22" t="s">
+      <c r="C36" s="20" t="s">
         <v>198</v>
       </c>
-      <c r="C35" s="22" t="s">
+      <c r="D36" s="21" t="s">
         <v>199</v>
       </c>
-      <c r="D35" s="23" t="s">
-        <v>200</v>
-      </c>
-      <c r="E35" s="23" t="s">
-        <v>201</v>
-      </c>
-      <c r="F35" s="23" t="s">
-        <v>37</v>
-      </c>
-      <c r="G35" s="23" t="s">
-        <v>202</v>
-      </c>
-      <c r="H35" s="23" t="s">
-        <v>203</v>
-      </c>
-      <c r="I35" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="J35" s="23" t="s">
-        <v>18</v>
-      </c>
-      <c r="K35" s="23" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="36" ht="24" customHeight="1" spans="1:11">
-      <c r="A36" s="31"/>
-      <c r="B36" s="20" t="s">
-        <v>205</v>
-      </c>
-      <c r="C36" s="20" t="s">
-        <v>206</v>
-      </c>
-      <c r="D36" s="21" t="s">
-        <v>207</v>
-      </c>
       <c r="E36" s="21" t="s">
-        <v>201</v>
+        <v>187</v>
       </c>
       <c r="F36" s="21" t="s">
         <v>37</v>
       </c>
       <c r="G36" s="21" t="s">
-        <v>202</v>
+        <v>188</v>
       </c>
       <c r="H36" s="21" t="s">
-        <v>203</v>
+        <v>189</v>
       </c>
       <c r="I36" s="21" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="J36" s="21" t="s">
         <v>18</v>
       </c>
       <c r="K36" s="21" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="37" ht="24" customHeight="1" spans="1:11">
+      <c r="A37" s="24"/>
+      <c r="B37" s="20" t="s">
+        <v>200</v>
+      </c>
+      <c r="C37" s="18" t="s">
+        <v>201</v>
+      </c>
+      <c r="D37" s="19" t="s">
+        <v>202</v>
+      </c>
+      <c r="E37" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="F37" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="G37" s="19" t="s">
+        <v>188</v>
+      </c>
+      <c r="H37" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="I37" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="J37" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="K37" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="38" ht="24" customHeight="1" spans="1:11">
+      <c r="A38" s="24"/>
+      <c r="B38" s="18" t="s">
+        <v>203</v>
+      </c>
+      <c r="C38" s="20" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="37" ht="24" customHeight="1" spans="1:11">
-      <c r="A37" s="31"/>
-      <c r="B37" s="22" t="s">
-        <v>208</v>
-      </c>
-      <c r="C37" s="22" t="s">
-        <v>209</v>
-      </c>
-      <c r="D37" s="23" t="s">
-        <v>210</v>
-      </c>
-      <c r="E37" s="23" t="s">
-        <v>201</v>
-      </c>
-      <c r="F37" s="23" t="s">
-        <v>37</v>
-      </c>
-      <c r="G37" s="23" t="s">
-        <v>202</v>
-      </c>
-      <c r="H37" s="23" t="s">
-        <v>203</v>
-      </c>
-      <c r="I37" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="J37" s="23" t="s">
-        <v>18</v>
-      </c>
-      <c r="K37" s="23" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="38" ht="24" customHeight="1" spans="1:11">
-      <c r="A38" s="31"/>
-      <c r="B38" s="20" t="s">
-        <v>211</v>
-      </c>
-      <c r="C38" s="20" t="s">
-        <v>212</v>
-      </c>
       <c r="D38" s="21" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="E38" s="21" t="s">
-        <v>201</v>
+        <v>187</v>
       </c>
       <c r="F38" s="21" t="s">
         <v>37</v>
       </c>
       <c r="G38" s="21" t="s">
-        <v>202</v>
+        <v>188</v>
       </c>
       <c r="H38" s="21" t="s">
-        <v>203</v>
+        <v>189</v>
       </c>
       <c r="I38" s="21" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="J38" s="21" t="s">
         <v>18</v>
       </c>
       <c r="K38" s="21" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
     </row>
     <row r="39" ht="24" customHeight="1" spans="1:11">
-      <c r="A39" s="31"/>
-      <c r="B39" s="22" t="s">
+      <c r="A39" s="24" t="s">
+        <v>206</v>
+      </c>
+      <c r="B39" s="20" t="s">
+        <v>207</v>
+      </c>
+      <c r="C39" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="D39" s="19" t="s">
+        <v>209</v>
+      </c>
+      <c r="E39" s="19" t="s">
+        <v>210</v>
+      </c>
+      <c r="F39" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="G39" s="19" t="s">
+        <v>188</v>
+      </c>
+      <c r="H39" s="19" t="s">
+        <v>211</v>
+      </c>
+      <c r="I39" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="J39" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="K39" s="19" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="40" ht="24" customHeight="1" spans="1:11">
+      <c r="A40" s="25"/>
+      <c r="B40" s="18" t="s">
+        <v>213</v>
+      </c>
+      <c r="C40" s="20" t="s">
         <v>214</v>
       </c>
-      <c r="C39" s="22" t="s">
+      <c r="D40" s="21" t="s">
         <v>215</v>
       </c>
-      <c r="D39" s="23" t="s">
-        <v>216</v>
-      </c>
-      <c r="E39" s="23" t="s">
-        <v>201</v>
-      </c>
-      <c r="F39" s="23" t="s">
-        <v>37</v>
-      </c>
-      <c r="G39" s="23" t="s">
-        <v>202</v>
-      </c>
-      <c r="H39" s="23" t="s">
-        <v>203</v>
-      </c>
-      <c r="I39" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="J39" s="23" t="s">
-        <v>18</v>
-      </c>
-      <c r="K39" s="23" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="40" ht="24" customHeight="1" spans="1:11">
-      <c r="A40" s="32"/>
-      <c r="B40" s="20" t="s">
-        <v>217</v>
-      </c>
-      <c r="C40" s="20" t="s">
-        <v>218</v>
-      </c>
-      <c r="D40" s="21" t="s">
-        <v>219</v>
-      </c>
       <c r="E40" s="21" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="F40" s="21" t="s">
         <v>37</v>
       </c>
       <c r="G40" s="21" t="s">
-        <v>202</v>
+        <v>188</v>
       </c>
       <c r="H40" s="21" t="s">
-        <v>203</v>
+        <v>216</v>
       </c>
       <c r="I40" s="21" t="s">
-        <v>125</v>
+        <v>217</v>
       </c>
       <c r="J40" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="K40" s="21" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="41" ht="24" customHeight="1" spans="1:11">
-      <c r="A41" s="33" t="s">
+      <c r="K40" s="21"/>
+    </row>
+    <row r="41" ht="36" customHeight="1" spans="1:11">
+      <c r="A41" s="25"/>
+      <c r="B41" s="20" t="s">
+        <v>218</v>
+      </c>
+      <c r="C41" s="18" t="s">
+        <v>219</v>
+      </c>
+      <c r="D41" s="19" t="s">
         <v>220</v>
       </c>
-      <c r="B41" s="22" t="s">
+      <c r="E41" s="19" t="s">
+        <v>210</v>
+      </c>
+      <c r="F41" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="G41" s="19" t="s">
+        <v>188</v>
+      </c>
+      <c r="H41" s="19" t="s">
+        <v>216</v>
+      </c>
+      <c r="I41" s="19" t="s">
         <v>221</v>
       </c>
-      <c r="C41" s="22" t="s">
+      <c r="J41" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="K41" s="19"/>
+    </row>
+    <row r="42" ht="36" customHeight="1" spans="1:11">
+      <c r="A42" s="25"/>
+      <c r="B42" s="18" t="s">
         <v>222</v>
       </c>
-      <c r="D41" s="23" t="s">
+      <c r="C42" s="20" t="s">
         <v>223</v>
       </c>
-      <c r="E41" s="23" t="s">
+      <c r="D42" s="21" t="s">
         <v>224</v>
       </c>
-      <c r="F41" s="23" t="s">
-        <v>37</v>
-      </c>
-      <c r="G41" s="23" t="s">
-        <v>202</v>
-      </c>
-      <c r="H41" s="23" t="s">
-        <v>225</v>
-      </c>
-      <c r="I41" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="J41" s="23" t="s">
-        <v>18</v>
-      </c>
-      <c r="K41" s="23" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="42" ht="36" customHeight="1" spans="1:11">
-      <c r="A42" s="34"/>
-      <c r="B42" s="20" t="s">
-        <v>227</v>
-      </c>
-      <c r="C42" s="20" t="s">
-        <v>228</v>
-      </c>
-      <c r="D42" s="21" t="s">
-        <v>229</v>
-      </c>
       <c r="E42" s="21" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="F42" s="21" t="s">
         <v>37</v>
       </c>
       <c r="G42" s="21" t="s">
-        <v>202</v>
+        <v>188</v>
       </c>
       <c r="H42" s="21" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="I42" s="21" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="J42" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="K42" s="21" t="s">
+      <c r="K42" s="21"/>
+    </row>
+    <row r="43" ht="36" customHeight="1" spans="1:11">
+      <c r="A43" s="25"/>
+      <c r="B43" s="20" t="s">
+        <v>226</v>
+      </c>
+      <c r="C43" s="18" t="s">
+        <v>227</v>
+      </c>
+      <c r="D43" s="19" t="s">
+        <v>228</v>
+      </c>
+      <c r="E43" s="19" t="s">
+        <v>210</v>
+      </c>
+      <c r="F43" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="G43" s="19" t="s">
+        <v>188</v>
+      </c>
+      <c r="H43" s="19" t="s">
+        <v>216</v>
+      </c>
+      <c r="I43" s="19" t="s">
+        <v>229</v>
+      </c>
+      <c r="J43" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="K43" s="19"/>
+    </row>
+    <row r="44" ht="36" customHeight="1" spans="1:11">
+      <c r="A44" s="25"/>
+      <c r="B44" s="18" t="s">
+        <v>230</v>
+      </c>
+      <c r="C44" s="20" t="s">
+        <v>231</v>
+      </c>
+      <c r="D44" s="21" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="43" ht="36" customHeight="1" spans="1:11">
-      <c r="A43" s="34"/>
-      <c r="B43" s="22" t="s">
-        <v>233</v>
-      </c>
-      <c r="C43" s="22" t="s">
-        <v>234</v>
-      </c>
-      <c r="D43" s="23" t="s">
-        <v>235</v>
-      </c>
-      <c r="E43" s="23" t="s">
-        <v>224</v>
-      </c>
-      <c r="F43" s="23" t="s">
-        <v>37</v>
-      </c>
-      <c r="G43" s="23" t="s">
-        <v>202</v>
-      </c>
-      <c r="H43" s="23" t="s">
-        <v>230</v>
-      </c>
-      <c r="I43" s="23" t="s">
-        <v>236</v>
-      </c>
-      <c r="J43" s="23" t="s">
-        <v>18</v>
-      </c>
-      <c r="K43" s="23" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="44" ht="36" customHeight="1" spans="1:11">
-      <c r="A44" s="34"/>
-      <c r="B44" s="20" t="s">
-        <v>237</v>
-      </c>
-      <c r="C44" s="20" t="s">
-        <v>238</v>
-      </c>
-      <c r="D44" s="21" t="s">
-        <v>239</v>
-      </c>
       <c r="E44" s="21" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="F44" s="21" t="s">
         <v>37</v>
       </c>
       <c r="G44" s="21" t="s">
-        <v>202</v>
+        <v>188</v>
       </c>
       <c r="H44" s="21" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="I44" s="21" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="J44" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="K44" s="21" t="s">
-        <v>232</v>
-      </c>
+      <c r="K44" s="21"/>
     </row>
     <row r="45" ht="36" customHeight="1" spans="1:11">
-      <c r="A45" s="34"/>
-      <c r="B45" s="22" t="s">
-        <v>241</v>
-      </c>
-      <c r="C45" s="22" t="s">
-        <v>242</v>
-      </c>
-      <c r="D45" s="23" t="s">
-        <v>243</v>
-      </c>
-      <c r="E45" s="23" t="s">
-        <v>224</v>
-      </c>
-      <c r="F45" s="23" t="s">
+      <c r="A45" s="25"/>
+      <c r="B45" s="20" t="s">
+        <v>234</v>
+      </c>
+      <c r="C45" s="18" t="s">
+        <v>235</v>
+      </c>
+      <c r="D45" s="19" t="s">
+        <v>236</v>
+      </c>
+      <c r="E45" s="19" t="s">
+        <v>210</v>
+      </c>
+      <c r="F45" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="G45" s="23" t="s">
-        <v>202</v>
-      </c>
-      <c r="H45" s="23" t="s">
-        <v>230</v>
-      </c>
-      <c r="I45" s="23" t="s">
-        <v>244</v>
-      </c>
-      <c r="J45" s="23" t="s">
+      <c r="G45" s="19" t="s">
+        <v>188</v>
+      </c>
+      <c r="H45" s="19" t="s">
+        <v>216</v>
+      </c>
+      <c r="I45" s="19" t="s">
+        <v>237</v>
+      </c>
+      <c r="J45" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="K45" s="23" t="s">
-        <v>232</v>
-      </c>
+      <c r="K45" s="19"/>
     </row>
     <row r="46" ht="36" customHeight="1" spans="1:11">
-      <c r="A46" s="34"/>
-      <c r="B46" s="20" t="s">
-        <v>245</v>
+      <c r="A46" s="25"/>
+      <c r="B46" s="18" t="s">
+        <v>238</v>
       </c>
       <c r="C46" s="20" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="D46" s="21" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="E46" s="21" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="F46" s="21" t="s">
         <v>37</v>
       </c>
       <c r="G46" s="21" t="s">
-        <v>202</v>
+        <v>188</v>
       </c>
       <c r="H46" s="21" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="I46" s="21" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="J46" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="K46" s="21" t="s">
-        <v>232</v>
-      </c>
+      <c r="K46" s="21"/>
     </row>
     <row r="47" ht="36" customHeight="1" spans="1:11">
-      <c r="A47" s="34"/>
-      <c r="B47" s="22" t="s">
-        <v>249</v>
-      </c>
-      <c r="C47" s="22" t="s">
-        <v>250</v>
-      </c>
-      <c r="D47" s="23" t="s">
-        <v>251</v>
-      </c>
-      <c r="E47" s="23" t="s">
-        <v>224</v>
-      </c>
-      <c r="F47" s="23" t="s">
+      <c r="A47" s="25"/>
+      <c r="B47" s="20" t="s">
+        <v>242</v>
+      </c>
+      <c r="C47" s="18" t="s">
+        <v>243</v>
+      </c>
+      <c r="D47" s="19" t="s">
+        <v>244</v>
+      </c>
+      <c r="E47" s="19" t="s">
+        <v>210</v>
+      </c>
+      <c r="F47" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="G47" s="23" t="s">
-        <v>202</v>
-      </c>
-      <c r="H47" s="23" t="s">
-        <v>230</v>
-      </c>
-      <c r="I47" s="23" t="s">
-        <v>252</v>
-      </c>
-      <c r="J47" s="23" t="s">
+      <c r="G47" s="19" t="s">
+        <v>188</v>
+      </c>
+      <c r="H47" s="19" t="s">
+        <v>216</v>
+      </c>
+      <c r="I47" s="19" t="s">
+        <v>245</v>
+      </c>
+      <c r="J47" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="K47" s="23" t="s">
-        <v>232</v>
-      </c>
+      <c r="K47" s="19"/>
     </row>
     <row r="48" ht="36" customHeight="1" spans="1:11">
-      <c r="A48" s="34"/>
-      <c r="B48" s="20" t="s">
-        <v>253</v>
+      <c r="A48" s="25"/>
+      <c r="B48" s="18" t="s">
+        <v>246</v>
       </c>
       <c r="C48" s="20" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="D48" s="21" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="E48" s="21" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="F48" s="21" t="s">
         <v>37</v>
       </c>
       <c r="G48" s="21" t="s">
-        <v>202</v>
+        <v>188</v>
       </c>
       <c r="H48" s="21" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="I48" s="21" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="J48" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="K48" s="21" t="s">
-        <v>232</v>
-      </c>
+      <c r="K48" s="21"/>
     </row>
     <row r="49" ht="36" customHeight="1" spans="1:11">
-      <c r="A49" s="34"/>
-      <c r="B49" s="22" t="s">
-        <v>257</v>
-      </c>
-      <c r="C49" s="22" t="s">
-        <v>258</v>
-      </c>
-      <c r="D49" s="23" t="s">
-        <v>259</v>
-      </c>
-      <c r="E49" s="23" t="s">
-        <v>224</v>
-      </c>
-      <c r="F49" s="23" t="s">
+      <c r="A49" s="25"/>
+      <c r="B49" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="C49" s="18" t="s">
+        <v>251</v>
+      </c>
+      <c r="D49" s="19" t="s">
+        <v>252</v>
+      </c>
+      <c r="E49" s="19" t="s">
+        <v>210</v>
+      </c>
+      <c r="F49" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="G49" s="23" t="s">
-        <v>202</v>
-      </c>
-      <c r="H49" s="23" t="s">
-        <v>230</v>
-      </c>
-      <c r="I49" s="23" t="s">
-        <v>260</v>
-      </c>
-      <c r="J49" s="23" t="s">
+      <c r="G49" s="19" t="s">
+        <v>188</v>
+      </c>
+      <c r="H49" s="19" t="s">
+        <v>216</v>
+      </c>
+      <c r="I49" s="19" t="s">
+        <v>253</v>
+      </c>
+      <c r="J49" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="K49" s="23" t="s">
-        <v>232</v>
-      </c>
+      <c r="K49" s="19"/>
     </row>
     <row r="50" ht="36" customHeight="1" spans="1:11">
-      <c r="A50" s="34"/>
-      <c r="B50" s="20" t="s">
-        <v>261</v>
+      <c r="A50" s="25"/>
+      <c r="B50" s="18" t="s">
+        <v>254</v>
       </c>
       <c r="C50" s="20" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="D50" s="21" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="E50" s="21" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="F50" s="21" t="s">
         <v>37</v>
       </c>
       <c r="G50" s="21" t="s">
-        <v>202</v>
+        <v>188</v>
       </c>
       <c r="H50" s="21" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="I50" s="21" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="J50" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="K50" s="21" t="s">
-        <v>232</v>
-      </c>
+      <c r="K50" s="21"/>
     </row>
     <row r="51" ht="36" customHeight="1" spans="1:11">
-      <c r="A51" s="34"/>
-      <c r="B51" s="22" t="s">
-        <v>265</v>
-      </c>
-      <c r="C51" s="22" t="s">
-        <v>266</v>
-      </c>
-      <c r="D51" s="23" t="s">
-        <v>267</v>
-      </c>
-      <c r="E51" s="23" t="s">
-        <v>224</v>
-      </c>
-      <c r="F51" s="23" t="s">
+      <c r="A51" s="25"/>
+      <c r="B51" s="20" t="s">
+        <v>258</v>
+      </c>
+      <c r="C51" s="18" t="s">
+        <v>259</v>
+      </c>
+      <c r="D51" s="19" t="s">
+        <v>260</v>
+      </c>
+      <c r="E51" s="19" t="s">
+        <v>210</v>
+      </c>
+      <c r="F51" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="G51" s="23" t="s">
-        <v>202</v>
-      </c>
-      <c r="H51" s="23" t="s">
-        <v>230</v>
-      </c>
-      <c r="I51" s="23" t="s">
-        <v>268</v>
-      </c>
-      <c r="J51" s="23" t="s">
+      <c r="G51" s="19" t="s">
+        <v>188</v>
+      </c>
+      <c r="H51" s="19" t="s">
+        <v>216</v>
+      </c>
+      <c r="I51" s="19" t="s">
+        <v>261</v>
+      </c>
+      <c r="J51" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="K51" s="23" t="s">
-        <v>232</v>
-      </c>
+      <c r="K51" s="19"/>
     </row>
     <row r="52" ht="36" customHeight="1" spans="1:11">
-      <c r="A52" s="34"/>
-      <c r="B52" s="20" t="s">
-        <v>269</v>
+      <c r="A52" s="25"/>
+      <c r="B52" s="18" t="s">
+        <v>262</v>
       </c>
       <c r="C52" s="20" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="D52" s="21" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="E52" s="21" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="F52" s="21" t="s">
         <v>37</v>
       </c>
       <c r="G52" s="21" t="s">
-        <v>202</v>
+        <v>188</v>
       </c>
       <c r="H52" s="21" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="I52" s="21" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="J52" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="K52" s="21" t="s">
-        <v>232</v>
-      </c>
+      <c r="K52" s="21"/>
     </row>
     <row r="53" ht="36" customHeight="1" spans="1:11">
-      <c r="A53" s="34"/>
-      <c r="B53" s="22" t="s">
-        <v>273</v>
-      </c>
-      <c r="C53" s="22" t="s">
-        <v>274</v>
-      </c>
-      <c r="D53" s="23" t="s">
-        <v>275</v>
-      </c>
-      <c r="E53" s="23" t="s">
-        <v>224</v>
-      </c>
-      <c r="F53" s="23" t="s">
+      <c r="A53" s="25"/>
+      <c r="B53" s="20" t="s">
+        <v>266</v>
+      </c>
+      <c r="C53" s="18" t="s">
+        <v>267</v>
+      </c>
+      <c r="D53" s="19" t="s">
+        <v>268</v>
+      </c>
+      <c r="E53" s="19" t="s">
+        <v>210</v>
+      </c>
+      <c r="F53" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="G53" s="23" t="s">
-        <v>202</v>
-      </c>
-      <c r="H53" s="23" t="s">
-        <v>230</v>
-      </c>
-      <c r="I53" s="23" t="s">
-        <v>276</v>
-      </c>
-      <c r="J53" s="23" t="s">
+      <c r="G53" s="19" t="s">
+        <v>188</v>
+      </c>
+      <c r="H53" s="19" t="s">
+        <v>216</v>
+      </c>
+      <c r="I53" s="19" t="s">
+        <v>269</v>
+      </c>
+      <c r="J53" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="K53" s="23" t="s">
-        <v>232</v>
-      </c>
+      <c r="K53" s="19"/>
     </row>
     <row r="54" ht="36" customHeight="1" spans="1:11">
-      <c r="A54" s="34"/>
-      <c r="B54" s="20" t="s">
-        <v>277</v>
+      <c r="A54" s="25"/>
+      <c r="B54" s="18" t="s">
+        <v>270</v>
       </c>
       <c r="C54" s="20" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="D54" s="21" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="E54" s="21" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="F54" s="21" t="s">
         <v>37</v>
       </c>
       <c r="G54" s="21" t="s">
-        <v>202</v>
+        <v>188</v>
       </c>
       <c r="H54" s="21" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="I54" s="21" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="J54" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="K54" s="21" t="s">
-        <v>232</v>
-      </c>
+      <c r="K54" s="21"/>
     </row>
     <row r="55" ht="36" customHeight="1" spans="1:11">
-      <c r="A55" s="34"/>
-      <c r="B55" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="C55" s="22" t="s">
-        <v>282</v>
-      </c>
-      <c r="D55" s="23" t="s">
-        <v>283</v>
-      </c>
-      <c r="E55" s="23" t="s">
-        <v>224</v>
-      </c>
-      <c r="F55" s="23" t="s">
+      <c r="A55" s="25"/>
+      <c r="B55" s="20" t="s">
+        <v>274</v>
+      </c>
+      <c r="C55" s="18" t="s">
+        <v>275</v>
+      </c>
+      <c r="D55" s="19" t="s">
+        <v>276</v>
+      </c>
+      <c r="E55" s="19" t="s">
+        <v>210</v>
+      </c>
+      <c r="F55" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="G55" s="23" t="s">
-        <v>202</v>
-      </c>
-      <c r="H55" s="23" t="s">
-        <v>230</v>
-      </c>
-      <c r="I55" s="23" t="s">
-        <v>284</v>
-      </c>
-      <c r="J55" s="23" t="s">
+      <c r="G55" s="19" t="s">
+        <v>188</v>
+      </c>
+      <c r="H55" s="19" t="s">
+        <v>216</v>
+      </c>
+      <c r="I55" s="19" t="s">
+        <v>277</v>
+      </c>
+      <c r="J55" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="K55" s="23" t="s">
-        <v>232</v>
-      </c>
+      <c r="K55" s="19"/>
     </row>
     <row r="56" ht="36" customHeight="1" spans="1:11">
-      <c r="A56" s="34"/>
-      <c r="B56" s="20" t="s">
-        <v>285</v>
+      <c r="A56" s="25"/>
+      <c r="B56" s="18" t="s">
+        <v>278</v>
       </c>
       <c r="C56" s="20" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="D56" s="21" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="E56" s="21" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="F56" s="21" t="s">
         <v>37</v>
       </c>
       <c r="G56" s="21" t="s">
-        <v>202</v>
+        <v>188</v>
       </c>
       <c r="H56" s="21" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="I56" s="21" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="J56" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="K56" s="21" t="s">
-        <v>232</v>
-      </c>
+      <c r="K56" s="21"/>
     </row>
     <row r="57" ht="36" customHeight="1" spans="1:11">
-      <c r="A57" s="34"/>
-      <c r="B57" s="22" t="s">
-        <v>289</v>
-      </c>
-      <c r="C57" s="22" t="s">
-        <v>290</v>
-      </c>
-      <c r="D57" s="23" t="s">
-        <v>291</v>
-      </c>
-      <c r="E57" s="23" t="s">
-        <v>224</v>
-      </c>
-      <c r="F57" s="23" t="s">
+      <c r="A57" s="25"/>
+      <c r="B57" s="20" t="s">
+        <v>282</v>
+      </c>
+      <c r="C57" s="18" t="s">
+        <v>283</v>
+      </c>
+      <c r="D57" s="19" t="s">
+        <v>284</v>
+      </c>
+      <c r="E57" s="19" t="s">
+        <v>210</v>
+      </c>
+      <c r="F57" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="G57" s="23" t="s">
-        <v>202</v>
-      </c>
-      <c r="H57" s="23" t="s">
-        <v>230</v>
-      </c>
-      <c r="I57" s="23" t="s">
-        <v>292</v>
-      </c>
-      <c r="J57" s="23" t="s">
+      <c r="G57" s="19" t="s">
+        <v>188</v>
+      </c>
+      <c r="H57" s="19" t="s">
+        <v>216</v>
+      </c>
+      <c r="I57" s="19" t="s">
+        <v>285</v>
+      </c>
+      <c r="J57" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="K57" s="23" t="s">
-        <v>232</v>
-      </c>
+      <c r="K57" s="19"/>
     </row>
     <row r="58" ht="36" customHeight="1" spans="1:11">
-      <c r="A58" s="34"/>
-      <c r="B58" s="20" t="s">
-        <v>293</v>
+      <c r="A58" s="25"/>
+      <c r="B58" s="18" t="s">
+        <v>286</v>
       </c>
       <c r="C58" s="20" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="D58" s="21" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="E58" s="21" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="F58" s="21" t="s">
         <v>37</v>
       </c>
       <c r="G58" s="21" t="s">
-        <v>202</v>
+        <v>188</v>
       </c>
       <c r="H58" s="21" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="I58" s="21" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="J58" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="K58" s="21" t="s">
-        <v>232</v>
-      </c>
+      <c r="K58" s="21"/>
     </row>
     <row r="59" ht="36" customHeight="1" spans="1:11">
-      <c r="A59" s="34"/>
-      <c r="B59" s="22" t="s">
-        <v>297</v>
-      </c>
-      <c r="C59" s="22" t="s">
-        <v>298</v>
-      </c>
-      <c r="D59" s="23" t="s">
-        <v>299</v>
-      </c>
-      <c r="E59" s="23" t="s">
-        <v>224</v>
-      </c>
-      <c r="F59" s="23" t="s">
+      <c r="A59" s="25"/>
+      <c r="B59" s="20" t="s">
+        <v>290</v>
+      </c>
+      <c r="C59" s="18" t="s">
+        <v>291</v>
+      </c>
+      <c r="D59" s="19" t="s">
+        <v>292</v>
+      </c>
+      <c r="E59" s="19" t="s">
+        <v>210</v>
+      </c>
+      <c r="F59" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="G59" s="23" t="s">
-        <v>202</v>
-      </c>
-      <c r="H59" s="23" t="s">
-        <v>230</v>
-      </c>
-      <c r="I59" s="23" t="s">
-        <v>300</v>
-      </c>
-      <c r="J59" s="23" t="s">
+      <c r="G59" s="19" t="s">
+        <v>188</v>
+      </c>
+      <c r="H59" s="19" t="s">
+        <v>216</v>
+      </c>
+      <c r="I59" s="19" t="s">
+        <v>293</v>
+      </c>
+      <c r="J59" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="K59" s="23" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="60" ht="36" customHeight="1" spans="1:11">
-      <c r="A60" s="34"/>
-      <c r="B60" s="20" t="s">
-        <v>301</v>
-      </c>
-      <c r="C60" s="20" t="s">
-        <v>302</v>
-      </c>
-      <c r="D60" s="21" t="s">
-        <v>303</v>
-      </c>
-      <c r="E60" s="21" t="s">
-        <v>224</v>
-      </c>
-      <c r="F60" s="21" t="s">
-        <v>37</v>
-      </c>
-      <c r="G60" s="21" t="s">
-        <v>202</v>
-      </c>
-      <c r="H60" s="21" t="s">
-        <v>230</v>
-      </c>
-      <c r="I60" s="21" t="s">
-        <v>304</v>
-      </c>
-      <c r="J60" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="K60" s="21" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="61" ht="36" customHeight="1" spans="1:11">
-      <c r="A61" s="35"/>
-      <c r="B61" s="22" t="s">
-        <v>305</v>
-      </c>
-      <c r="C61" s="22" t="s">
-        <v>306</v>
-      </c>
-      <c r="D61" s="23" t="s">
-        <v>307</v>
-      </c>
-      <c r="E61" s="23" t="s">
-        <v>224</v>
-      </c>
-      <c r="F61" s="23" t="s">
-        <v>37</v>
-      </c>
-      <c r="G61" s="23" t="s">
-        <v>202</v>
-      </c>
-      <c r="H61" s="23" t="s">
-        <v>230</v>
-      </c>
-      <c r="I61" s="23" t="s">
-        <v>308</v>
-      </c>
-      <c r="J61" s="23" t="s">
-        <v>18</v>
-      </c>
-      <c r="K61" s="23" t="s">
-        <v>232</v>
-      </c>
+      <c r="K59" s="19"/>
+    </row>
+    <row r="60" ht="36" customHeight="1" spans="1:2">
+      <c r="A60" s="15"/>
+      <c r="B60" s="15"/>
+    </row>
+    <row r="61" spans="1:11">
+      <c r="A61" s="15"/>
+      <c r="B61" s="15"/>
+      <c r="C61" s="15"/>
+      <c r="D61" s="15"/>
+      <c r="E61" s="15"/>
+      <c r="F61" s="15"/>
+      <c r="G61" s="15"/>
+      <c r="H61" s="15"/>
+      <c r="I61" s="15"/>
+      <c r="J61" s="15"/>
+      <c r="K61" s="15"/>
     </row>
     <row r="62" spans="1:11">
-      <c r="A62" s="17"/>
-      <c r="B62" s="17"/>
-      <c r="C62" s="17"/>
-      <c r="D62" s="17"/>
-      <c r="E62" s="17"/>
-      <c r="F62" s="17"/>
-      <c r="G62" s="17"/>
-      <c r="H62" s="17"/>
-      <c r="I62" s="17"/>
-      <c r="J62" s="17"/>
-      <c r="K62" s="17"/>
+      <c r="A62" s="15"/>
+      <c r="B62" s="15"/>
+      <c r="C62" s="15"/>
+      <c r="D62" s="15"/>
+      <c r="E62" s="15"/>
+      <c r="F62" s="15"/>
+      <c r="G62" s="15"/>
+      <c r="H62" s="15"/>
+      <c r="I62" s="15"/>
+      <c r="J62" s="15"/>
+      <c r="K62" s="15"/>
     </row>
     <row r="63" spans="1:11">
-      <c r="A63" s="17"/>
-      <c r="B63" s="17"/>
-      <c r="C63" s="17"/>
-      <c r="D63" s="17"/>
-      <c r="E63" s="17"/>
-      <c r="F63" s="17"/>
-      <c r="G63" s="17"/>
-      <c r="H63" s="17"/>
-      <c r="I63" s="17"/>
-      <c r="J63" s="17"/>
-      <c r="K63" s="17"/>
+      <c r="A63" s="15"/>
+      <c r="B63" s="15"/>
+      <c r="C63" s="15"/>
+      <c r="D63" s="15"/>
+      <c r="E63" s="15"/>
+      <c r="F63" s="15"/>
+      <c r="G63" s="15"/>
+      <c r="H63" s="15"/>
+      <c r="I63" s="15"/>
+      <c r="J63" s="15"/>
+      <c r="K63" s="15"/>
     </row>
     <row r="64" spans="1:11">
-      <c r="A64" s="17"/>
-      <c r="B64" s="17"/>
-      <c r="C64" s="17"/>
-      <c r="D64" s="17"/>
-      <c r="E64" s="17"/>
-      <c r="F64" s="17"/>
-      <c r="G64" s="17"/>
-      <c r="H64" s="17"/>
-      <c r="I64" s="17"/>
-      <c r="J64" s="17"/>
-      <c r="K64" s="17"/>
+      <c r="A64" s="15"/>
+      <c r="B64" s="15"/>
+      <c r="C64" s="15"/>
+      <c r="D64" s="15"/>
+      <c r="E64" s="15"/>
+      <c r="F64" s="15"/>
+      <c r="G64" s="15"/>
+      <c r="H64" s="15"/>
+      <c r="I64" s="15"/>
+      <c r="J64" s="15"/>
+      <c r="K64" s="15"/>
     </row>
     <row r="65" spans="1:11">
-      <c r="A65" s="17"/>
-      <c r="B65" s="17"/>
-      <c r="C65" s="17"/>
-      <c r="D65" s="17"/>
-      <c r="E65" s="17"/>
-      <c r="F65" s="17"/>
-      <c r="G65" s="17"/>
-      <c r="H65" s="17"/>
-      <c r="I65" s="17"/>
-      <c r="J65" s="17"/>
-      <c r="K65" s="17"/>
+      <c r="A65" s="15"/>
+      <c r="B65" s="15"/>
+      <c r="C65" s="15"/>
+      <c r="D65" s="15"/>
+      <c r="E65" s="15"/>
+      <c r="F65" s="15"/>
+      <c r="G65" s="15"/>
+      <c r="H65" s="15"/>
+      <c r="I65" s="15"/>
+      <c r="J65" s="15"/>
+      <c r="K65" s="15"/>
     </row>
     <row r="66" spans="1:11">
-      <c r="A66" s="17"/>
-      <c r="B66" s="17"/>
-      <c r="C66" s="17"/>
-      <c r="D66" s="17"/>
-      <c r="E66" s="17"/>
-      <c r="F66" s="17"/>
-      <c r="G66" s="17"/>
-      <c r="H66" s="17"/>
-      <c r="I66" s="17"/>
-      <c r="J66" s="17"/>
-      <c r="K66" s="17"/>
+      <c r="A66" s="15"/>
+      <c r="B66" s="15"/>
+      <c r="C66" s="15"/>
+      <c r="D66" s="15"/>
+      <c r="E66" s="15"/>
+      <c r="F66" s="15"/>
+      <c r="G66" s="15"/>
+      <c r="H66" s="15"/>
+      <c r="I66" s="15"/>
+      <c r="J66" s="15"/>
+      <c r="K66" s="15"/>
     </row>
     <row r="67" spans="1:11">
-      <c r="A67" s="17"/>
-      <c r="B67" s="17"/>
-      <c r="C67" s="17"/>
-      <c r="D67" s="17"/>
-      <c r="E67" s="17"/>
-      <c r="F67" s="17"/>
-      <c r="G67" s="17"/>
-      <c r="H67" s="17"/>
-      <c r="I67" s="17"/>
-      <c r="J67" s="17"/>
-      <c r="K67" s="17"/>
+      <c r="A67" s="15"/>
+      <c r="B67" s="15"/>
+      <c r="C67" s="15"/>
+      <c r="D67" s="15"/>
+      <c r="E67" s="15"/>
+      <c r="F67" s="15"/>
+      <c r="G67" s="15"/>
+      <c r="H67" s="15"/>
+      <c r="I67" s="15"/>
+      <c r="J67" s="15"/>
+      <c r="K67" s="15"/>
     </row>
     <row r="68" spans="1:11">
-      <c r="A68" s="17"/>
-      <c r="B68" s="17"/>
-      <c r="C68" s="17"/>
-      <c r="D68" s="17"/>
-      <c r="E68" s="17"/>
-      <c r="F68" s="17"/>
-      <c r="G68" s="17"/>
-      <c r="H68" s="17"/>
-      <c r="I68" s="17"/>
-      <c r="J68" s="17"/>
-      <c r="K68" s="17"/>
+      <c r="A68" s="15"/>
+      <c r="B68" s="15"/>
+      <c r="C68" s="15"/>
+      <c r="D68" s="15"/>
+      <c r="E68" s="15"/>
+      <c r="F68" s="15"/>
+      <c r="G68" s="15"/>
+      <c r="H68" s="15"/>
+      <c r="I68" s="15"/>
+      <c r="J68" s="15"/>
+      <c r="K68" s="15"/>
     </row>
     <row r="69" spans="1:11">
-      <c r="A69" s="17"/>
-      <c r="B69" s="17"/>
-      <c r="C69" s="17"/>
-      <c r="D69" s="17"/>
-      <c r="E69" s="17"/>
-      <c r="F69" s="17"/>
-      <c r="G69" s="17"/>
-      <c r="H69" s="17"/>
-      <c r="I69" s="17"/>
-      <c r="J69" s="17"/>
-      <c r="K69" s="17"/>
+      <c r="A69" s="15"/>
+      <c r="B69" s="15"/>
+      <c r="C69" s="15"/>
+      <c r="D69" s="15"/>
+      <c r="E69" s="15"/>
+      <c r="F69" s="15"/>
+      <c r="G69" s="15"/>
+      <c r="H69" s="15"/>
+      <c r="I69" s="15"/>
+      <c r="J69" s="15"/>
+      <c r="K69" s="15"/>
     </row>
     <row r="70" spans="1:11">
-      <c r="A70" s="17"/>
-      <c r="B70" s="17"/>
-      <c r="C70" s="17"/>
-      <c r="D70" s="17"/>
-      <c r="E70" s="17"/>
-      <c r="F70" s="17"/>
-      <c r="G70" s="17"/>
-      <c r="H70" s="17"/>
-      <c r="I70" s="17"/>
-      <c r="J70" s="17"/>
-      <c r="K70" s="17"/>
+      <c r="A70" s="15"/>
+      <c r="B70" s="15"/>
+      <c r="C70" s="15"/>
+      <c r="D70" s="15"/>
+      <c r="E70" s="15"/>
+      <c r="F70" s="15"/>
+      <c r="G70" s="15"/>
+      <c r="H70" s="15"/>
+      <c r="I70" s="15"/>
+      <c r="J70" s="15"/>
+      <c r="K70" s="15"/>
     </row>
     <row r="71" spans="1:11">
-      <c r="A71" s="17"/>
-      <c r="B71" s="17"/>
-      <c r="C71" s="17"/>
-      <c r="D71" s="17"/>
-      <c r="E71" s="17"/>
-      <c r="F71" s="17"/>
-      <c r="G71" s="17"/>
-      <c r="H71" s="17"/>
-      <c r="I71" s="17"/>
-      <c r="J71" s="17"/>
-      <c r="K71" s="17"/>
+      <c r="A71" s="15"/>
+      <c r="B71" s="15"/>
+      <c r="C71" s="15"/>
+      <c r="D71" s="15"/>
+      <c r="E71" s="15"/>
+      <c r="F71" s="15"/>
+      <c r="G71" s="15"/>
+      <c r="H71" s="15"/>
+      <c r="I71" s="15"/>
+      <c r="J71" s="15"/>
+      <c r="K71" s="15"/>
     </row>
     <row r="72" spans="1:11">
-      <c r="A72" s="17"/>
-      <c r="B72" s="17"/>
-      <c r="C72" s="17"/>
-      <c r="D72" s="17"/>
-      <c r="E72" s="17"/>
-      <c r="F72" s="17"/>
-      <c r="G72" s="17"/>
-      <c r="H72" s="17"/>
-      <c r="I72" s="17"/>
-      <c r="J72" s="17"/>
-      <c r="K72" s="17"/>
+      <c r="A72" s="15"/>
+      <c r="B72" s="15"/>
+      <c r="C72" s="15"/>
+      <c r="D72" s="15"/>
+      <c r="E72" s="15"/>
+      <c r="F72" s="15"/>
+      <c r="G72" s="15"/>
+      <c r="H72" s="15"/>
+      <c r="I72" s="15"/>
+      <c r="J72" s="15"/>
+      <c r="K72" s="15"/>
     </row>
     <row r="73" spans="1:11">
-      <c r="A73" s="17"/>
-      <c r="B73" s="17"/>
-      <c r="C73" s="17"/>
-      <c r="D73" s="17"/>
-      <c r="E73" s="17"/>
-      <c r="F73" s="17"/>
-      <c r="G73" s="17"/>
-      <c r="H73" s="17"/>
-      <c r="I73" s="17"/>
-      <c r="J73" s="17"/>
-      <c r="K73" s="17"/>
+      <c r="A73" s="15"/>
+      <c r="B73" s="15"/>
+      <c r="C73" s="15"/>
+      <c r="D73" s="15"/>
+      <c r="E73" s="15"/>
+      <c r="F73" s="15"/>
+      <c r="G73" s="15"/>
+      <c r="H73" s="15"/>
+      <c r="I73" s="15"/>
+      <c r="J73" s="15"/>
+      <c r="K73" s="15"/>
     </row>
     <row r="74" spans="1:11">
-      <c r="A74" s="17"/>
-      <c r="B74" s="17"/>
-      <c r="C74" s="17"/>
-      <c r="D74" s="17"/>
-      <c r="E74" s="17"/>
-      <c r="F74" s="17"/>
-      <c r="G74" s="17"/>
-      <c r="H74" s="17"/>
-      <c r="I74" s="17"/>
-      <c r="J74" s="17"/>
-      <c r="K74" s="17"/>
+      <c r="A74" s="15"/>
+      <c r="B74" s="15"/>
+      <c r="C74" s="15"/>
+      <c r="D74" s="15"/>
+      <c r="E74" s="15"/>
+      <c r="F74" s="15"/>
+      <c r="G74" s="15"/>
+      <c r="H74" s="15"/>
+      <c r="I74" s="15"/>
+      <c r="J74" s="15"/>
+      <c r="K74" s="15"/>
     </row>
     <row r="75" spans="1:11">
-      <c r="A75" s="17"/>
-      <c r="B75" s="17"/>
-      <c r="C75" s="17"/>
-      <c r="D75" s="17"/>
-      <c r="E75" s="17"/>
-      <c r="F75" s="17"/>
-      <c r="G75" s="17"/>
-      <c r="H75" s="17"/>
-      <c r="I75" s="17"/>
-      <c r="J75" s="17"/>
-      <c r="K75" s="17"/>
+      <c r="A75" s="15"/>
+      <c r="B75" s="15"/>
+      <c r="C75" s="15"/>
+      <c r="D75" s="15"/>
+      <c r="E75" s="15"/>
+      <c r="F75" s="15"/>
+      <c r="G75" s="15"/>
+      <c r="H75" s="15"/>
+      <c r="I75" s="15"/>
+      <c r="J75" s="15"/>
+      <c r="K75" s="15"/>
     </row>
     <row r="76" spans="1:11">
-      <c r="A76" s="17"/>
-      <c r="B76" s="17"/>
-      <c r="C76" s="17"/>
-      <c r="D76" s="17"/>
-      <c r="E76" s="17"/>
-      <c r="F76" s="17"/>
-      <c r="G76" s="17"/>
-      <c r="H76" s="17"/>
-      <c r="I76" s="17"/>
-      <c r="J76" s="17"/>
-      <c r="K76" s="17"/>
+      <c r="A76" s="15"/>
+      <c r="B76" s="15"/>
+      <c r="C76" s="15"/>
+      <c r="D76" s="15"/>
+      <c r="E76" s="15"/>
+      <c r="F76" s="15"/>
+      <c r="G76" s="15"/>
+      <c r="H76" s="15"/>
+      <c r="I76" s="15"/>
+      <c r="J76" s="15"/>
+      <c r="K76" s="15"/>
     </row>
     <row r="77" spans="1:11">
-      <c r="A77" s="17"/>
-      <c r="B77" s="17"/>
-      <c r="C77" s="17"/>
-      <c r="D77" s="17"/>
-      <c r="E77" s="17"/>
-      <c r="F77" s="17"/>
-      <c r="G77" s="17"/>
-      <c r="H77" s="17"/>
-      <c r="I77" s="17"/>
-      <c r="J77" s="17"/>
-      <c r="K77" s="17"/>
+      <c r="A77" s="15"/>
+      <c r="B77" s="15"/>
+      <c r="C77" s="15"/>
+      <c r="D77" s="15"/>
+      <c r="E77" s="15"/>
+      <c r="F77" s="15"/>
+      <c r="G77" s="15"/>
+      <c r="H77" s="15"/>
+      <c r="I77" s="15"/>
+      <c r="J77" s="15"/>
+      <c r="K77" s="15"/>
     </row>
     <row r="78" spans="1:11">
-      <c r="A78" s="17"/>
-      <c r="B78" s="17"/>
-      <c r="C78" s="17"/>
-      <c r="D78" s="17"/>
-      <c r="E78" s="17"/>
-      <c r="F78" s="17"/>
-      <c r="G78" s="17"/>
-      <c r="H78" s="17"/>
-      <c r="I78" s="17"/>
-      <c r="J78" s="17"/>
-      <c r="K78" s="17"/>
+      <c r="A78" s="15"/>
+      <c r="B78" s="15"/>
+      <c r="C78" s="15"/>
+      <c r="D78" s="15"/>
+      <c r="E78" s="15"/>
+      <c r="F78" s="15"/>
+      <c r="G78" s="15"/>
+      <c r="H78" s="15"/>
+      <c r="I78" s="15"/>
+      <c r="J78" s="15"/>
+      <c r="K78" s="15"/>
     </row>
     <row r="79" spans="1:11">
-      <c r="A79" s="17"/>
-      <c r="B79" s="17"/>
-      <c r="C79" s="17"/>
-      <c r="D79" s="17"/>
-      <c r="E79" s="17"/>
-      <c r="F79" s="17"/>
-      <c r="G79" s="17"/>
-      <c r="H79" s="17"/>
-      <c r="I79" s="17"/>
-      <c r="J79" s="17"/>
-      <c r="K79" s="17"/>
+      <c r="A79" s="15"/>
+      <c r="B79" s="15"/>
+      <c r="C79" s="15"/>
+      <c r="D79" s="15"/>
+      <c r="E79" s="15"/>
+      <c r="F79" s="15"/>
+      <c r="G79" s="15"/>
+      <c r="H79" s="15"/>
+      <c r="I79" s="15"/>
+      <c r="J79" s="15"/>
+      <c r="K79" s="15"/>
     </row>
     <row r="80" spans="1:11">
-      <c r="A80" s="17"/>
-      <c r="B80" s="17"/>
-      <c r="C80" s="17"/>
-      <c r="D80" s="17"/>
-      <c r="E80" s="17"/>
-      <c r="F80" s="17"/>
-      <c r="G80" s="17"/>
-      <c r="H80" s="17"/>
-      <c r="I80" s="17"/>
-      <c r="J80" s="17"/>
-      <c r="K80" s="17"/>
+      <c r="A80" s="15"/>
+      <c r="B80" s="15"/>
+      <c r="C80" s="15"/>
+      <c r="D80" s="15"/>
+      <c r="E80" s="15"/>
+      <c r="F80" s="15"/>
+      <c r="G80" s="15"/>
+      <c r="H80" s="15"/>
+      <c r="I80" s="15"/>
+      <c r="J80" s="15"/>
+      <c r="K80" s="15"/>
     </row>
     <row r="81" spans="1:11">
-      <c r="A81" s="17"/>
-      <c r="B81" s="17"/>
-      <c r="C81" s="17"/>
-      <c r="D81" s="17"/>
-      <c r="E81" s="17"/>
-      <c r="F81" s="17"/>
-      <c r="G81" s="17"/>
-      <c r="H81" s="17"/>
-      <c r="I81" s="17"/>
-      <c r="J81" s="17"/>
-      <c r="K81" s="17"/>
+      <c r="A81" s="15"/>
+      <c r="B81" s="15"/>
+      <c r="C81" s="15"/>
+      <c r="D81" s="15"/>
+      <c r="E81" s="15"/>
+      <c r="F81" s="15"/>
+      <c r="G81" s="15"/>
+      <c r="H81" s="15"/>
+      <c r="I81" s="15"/>
+      <c r="J81" s="15"/>
+      <c r="K81" s="15"/>
     </row>
     <row r="82" spans="1:11">
-      <c r="A82" s="17"/>
-      <c r="B82" s="17"/>
-      <c r="C82" s="17"/>
-      <c r="D82" s="17"/>
-      <c r="E82" s="17"/>
-      <c r="F82" s="17"/>
-      <c r="G82" s="17"/>
-      <c r="H82" s="17"/>
-      <c r="I82" s="17"/>
-      <c r="J82" s="17"/>
-      <c r="K82" s="17"/>
+      <c r="A82" s="15"/>
+      <c r="B82" s="15"/>
+      <c r="C82" s="15"/>
+      <c r="D82" s="15"/>
+      <c r="E82" s="15"/>
+      <c r="F82" s="15"/>
+      <c r="G82" s="15"/>
+      <c r="H82" s="15"/>
+      <c r="I82" s="15"/>
+      <c r="J82" s="15"/>
+      <c r="K82" s="15"/>
     </row>
     <row r="83" spans="1:11">
-      <c r="A83" s="17"/>
-      <c r="B83" s="17"/>
-      <c r="C83" s="17"/>
-      <c r="D83" s="17"/>
-      <c r="E83" s="17"/>
-      <c r="F83" s="17"/>
-      <c r="G83" s="17"/>
-      <c r="H83" s="17"/>
-      <c r="I83" s="17"/>
-      <c r="J83" s="17"/>
-      <c r="K83" s="17"/>
+      <c r="A83" s="15"/>
+      <c r="B83" s="15"/>
+      <c r="C83" s="15"/>
+      <c r="D83" s="15"/>
+      <c r="E83" s="15"/>
+      <c r="F83" s="15"/>
+      <c r="G83" s="15"/>
+      <c r="H83" s="15"/>
+      <c r="I83" s="15"/>
+      <c r="J83" s="15"/>
+      <c r="K83" s="15"/>
     </row>
     <row r="84" spans="1:11">
-      <c r="A84" s="17"/>
-      <c r="B84" s="17"/>
-      <c r="C84" s="17"/>
-      <c r="D84" s="17"/>
-      <c r="E84" s="17"/>
-      <c r="F84" s="17"/>
-      <c r="G84" s="17"/>
-      <c r="H84" s="17"/>
-      <c r="I84" s="17"/>
-      <c r="J84" s="17"/>
-      <c r="K84" s="17"/>
+      <c r="A84" s="15"/>
+      <c r="B84" s="15"/>
+      <c r="C84" s="15"/>
+      <c r="D84" s="15"/>
+      <c r="E84" s="15"/>
+      <c r="F84" s="15"/>
+      <c r="G84" s="15"/>
+      <c r="H84" s="15"/>
+      <c r="I84" s="15"/>
+      <c r="J84" s="15"/>
+      <c r="K84" s="15"/>
     </row>
     <row r="85" spans="1:11">
-      <c r="A85" s="17"/>
-      <c r="B85" s="17"/>
-      <c r="C85" s="17"/>
-      <c r="D85" s="17"/>
-      <c r="E85" s="17"/>
-      <c r="F85" s="17"/>
-      <c r="G85" s="17"/>
-      <c r="H85" s="17"/>
-      <c r="I85" s="17"/>
-      <c r="J85" s="17"/>
-      <c r="K85" s="17"/>
+      <c r="A85" s="15"/>
+      <c r="B85" s="15"/>
+      <c r="C85" s="15"/>
+      <c r="D85" s="15"/>
+      <c r="E85" s="15"/>
+      <c r="F85" s="15"/>
+      <c r="G85" s="15"/>
+      <c r="H85" s="15"/>
+      <c r="I85" s="15"/>
+      <c r="J85" s="15"/>
+      <c r="K85" s="15"/>
     </row>
     <row r="86" spans="1:11">
-      <c r="A86" s="17"/>
-      <c r="B86" s="17"/>
-      <c r="C86" s="17"/>
-      <c r="D86" s="17"/>
-      <c r="E86" s="17"/>
-      <c r="F86" s="17"/>
-      <c r="G86" s="17"/>
-      <c r="H86" s="17"/>
-      <c r="I86" s="17"/>
-      <c r="J86" s="17"/>
-      <c r="K86" s="17"/>
+      <c r="A86" s="15"/>
+      <c r="B86" s="15"/>
+      <c r="C86" s="15"/>
+      <c r="D86" s="15"/>
+      <c r="E86" s="15"/>
+      <c r="F86" s="15"/>
+      <c r="G86" s="15"/>
+      <c r="H86" s="15"/>
+      <c r="I86" s="15"/>
+      <c r="J86" s="15"/>
+      <c r="K86" s="15"/>
     </row>
     <row r="87" spans="1:11">
-      <c r="A87" s="17"/>
-      <c r="B87" s="17"/>
-      <c r="C87" s="17"/>
-      <c r="D87" s="17"/>
-      <c r="E87" s="17"/>
-      <c r="F87" s="17"/>
-      <c r="G87" s="17"/>
-      <c r="H87" s="17"/>
-      <c r="I87" s="17"/>
-      <c r="J87" s="17"/>
-      <c r="K87" s="17"/>
+      <c r="A87" s="15"/>
+      <c r="B87" s="15"/>
+      <c r="C87" s="15"/>
+      <c r="D87" s="15"/>
+      <c r="E87" s="15"/>
+      <c r="F87" s="15"/>
+      <c r="G87" s="15"/>
+      <c r="H87" s="15"/>
+      <c r="I87" s="15"/>
+      <c r="J87" s="15"/>
+      <c r="K87" s="15"/>
     </row>
     <row r="88" spans="1:11">
-      <c r="A88" s="17"/>
-      <c r="B88" s="17"/>
-      <c r="C88" s="17"/>
-      <c r="D88" s="17"/>
-      <c r="E88" s="17"/>
-      <c r="F88" s="17"/>
-      <c r="G88" s="17"/>
-      <c r="H88" s="17"/>
-      <c r="I88" s="17"/>
-      <c r="J88" s="17"/>
-      <c r="K88" s="17"/>
+      <c r="A88" s="15"/>
+      <c r="B88" s="15"/>
+      <c r="C88" s="15"/>
+      <c r="D88" s="15"/>
+      <c r="E88" s="15"/>
+      <c r="F88" s="15"/>
+      <c r="G88" s="15"/>
+      <c r="H88" s="15"/>
+      <c r="I88" s="15"/>
+      <c r="J88" s="15"/>
+      <c r="K88" s="15"/>
     </row>
     <row r="89" spans="1:11">
-      <c r="A89" s="17"/>
-      <c r="B89" s="17"/>
-      <c r="C89" s="17"/>
-      <c r="D89" s="17"/>
-      <c r="E89" s="17"/>
-      <c r="F89" s="17"/>
-      <c r="G89" s="17"/>
-      <c r="H89" s="17"/>
-      <c r="I89" s="17"/>
-      <c r="J89" s="17"/>
-      <c r="K89" s="17"/>
+      <c r="A89" s="15"/>
+      <c r="B89" s="15"/>
+      <c r="C89" s="15"/>
+      <c r="D89" s="15"/>
+      <c r="E89" s="15"/>
+      <c r="F89" s="15"/>
+      <c r="G89" s="15"/>
+      <c r="H89" s="15"/>
+      <c r="I89" s="15"/>
+      <c r="J89" s="15"/>
+      <c r="K89" s="15"/>
     </row>
     <row r="90" spans="1:11">
-      <c r="A90" s="17"/>
-      <c r="B90" s="17"/>
-      <c r="C90" s="17"/>
-      <c r="D90" s="17"/>
-      <c r="E90" s="17"/>
-      <c r="F90" s="17"/>
-      <c r="G90" s="17"/>
-      <c r="H90" s="17"/>
-      <c r="I90" s="17"/>
-      <c r="J90" s="17"/>
-      <c r="K90" s="17"/>
+      <c r="A90" s="15"/>
+      <c r="B90" s="15"/>
+      <c r="C90" s="15"/>
+      <c r="D90" s="15"/>
+      <c r="E90" s="15"/>
+      <c r="F90" s="15"/>
+      <c r="G90" s="15"/>
+      <c r="H90" s="15"/>
+      <c r="I90" s="15"/>
+      <c r="J90" s="15"/>
+      <c r="K90" s="15"/>
     </row>
     <row r="91" spans="1:11">
-      <c r="A91" s="17"/>
-      <c r="B91" s="17"/>
-      <c r="C91" s="17"/>
-      <c r="D91" s="17"/>
-      <c r="E91" s="17"/>
-      <c r="F91" s="17"/>
-      <c r="G91" s="17"/>
-      <c r="H91" s="17"/>
-      <c r="I91" s="17"/>
-      <c r="J91" s="17"/>
-      <c r="K91" s="17"/>
+      <c r="A91" s="15"/>
+      <c r="B91" s="15"/>
+      <c r="C91" s="15"/>
+      <c r="D91" s="15"/>
+      <c r="E91" s="15"/>
+      <c r="F91" s="15"/>
+      <c r="G91" s="15"/>
+      <c r="H91" s="15"/>
+      <c r="I91" s="15"/>
+      <c r="J91" s="15"/>
+      <c r="K91" s="15"/>
     </row>
     <row r="92" spans="1:11">
-      <c r="A92" s="17"/>
-      <c r="B92" s="17"/>
-      <c r="C92" s="17"/>
-      <c r="D92" s="17"/>
-      <c r="E92" s="17"/>
-      <c r="F92" s="17"/>
-      <c r="G92" s="17"/>
-      <c r="H92" s="17"/>
-      <c r="I92" s="17"/>
-      <c r="J92" s="17"/>
-      <c r="K92" s="17"/>
+      <c r="A92" s="15"/>
+      <c r="B92" s="15"/>
+      <c r="C92" s="15"/>
+      <c r="D92" s="15"/>
+      <c r="E92" s="15"/>
+      <c r="F92" s="15"/>
+      <c r="G92" s="15"/>
+      <c r="H92" s="15"/>
+      <c r="I92" s="15"/>
+      <c r="J92" s="15"/>
+      <c r="K92" s="15"/>
     </row>
     <row r="93" spans="1:11">
-      <c r="A93" s="17"/>
-      <c r="B93" s="17"/>
-      <c r="C93" s="17"/>
-      <c r="D93" s="17"/>
-      <c r="E93" s="17"/>
-      <c r="F93" s="17"/>
-      <c r="G93" s="17"/>
-      <c r="H93" s="17"/>
-      <c r="I93" s="17"/>
-      <c r="J93" s="17"/>
-      <c r="K93" s="17"/>
+      <c r="A93" s="15"/>
+      <c r="B93" s="15"/>
+      <c r="C93" s="15"/>
+      <c r="D93" s="15"/>
+      <c r="E93" s="15"/>
+      <c r="F93" s="15"/>
+      <c r="G93" s="15"/>
+      <c r="H93" s="15"/>
+      <c r="I93" s="15"/>
+      <c r="J93" s="15"/>
+      <c r="K93" s="15"/>
     </row>
     <row r="94" spans="1:11">
-      <c r="A94" s="17"/>
-      <c r="B94" s="17"/>
-      <c r="C94" s="17"/>
-      <c r="D94" s="17"/>
-      <c r="E94" s="17"/>
-      <c r="F94" s="17"/>
-      <c r="G94" s="17"/>
-      <c r="H94" s="17"/>
-      <c r="I94" s="17"/>
-      <c r="J94" s="17"/>
-      <c r="K94" s="17"/>
+      <c r="A94" s="15"/>
+      <c r="B94" s="15"/>
+      <c r="C94" s="15"/>
+      <c r="D94" s="15"/>
+      <c r="E94" s="15"/>
+      <c r="F94" s="15"/>
+      <c r="G94" s="15"/>
+      <c r="H94" s="15"/>
+      <c r="I94" s="15"/>
+      <c r="J94" s="15"/>
+      <c r="K94" s="15"/>
     </row>
     <row r="95" spans="1:11">
-      <c r="A95" s="17"/>
-      <c r="B95" s="17"/>
-      <c r="C95" s="17"/>
-      <c r="D95" s="17"/>
-      <c r="E95" s="17"/>
-      <c r="F95" s="17"/>
-      <c r="G95" s="17"/>
-      <c r="H95" s="17"/>
-      <c r="I95" s="17"/>
-      <c r="J95" s="17"/>
-      <c r="K95" s="17"/>
+      <c r="A95" s="15"/>
+      <c r="B95" s="15"/>
+      <c r="C95" s="15"/>
+      <c r="D95" s="15"/>
+      <c r="E95" s="15"/>
+      <c r="F95" s="15"/>
+      <c r="G95" s="15"/>
+      <c r="H95" s="15"/>
+      <c r="I95" s="15"/>
+      <c r="J95" s="15"/>
+      <c r="K95" s="15"/>
     </row>
     <row r="96" spans="1:11">
-      <c r="A96" s="17"/>
-      <c r="B96" s="17"/>
-      <c r="C96" s="17"/>
-      <c r="D96" s="17"/>
-      <c r="E96" s="17"/>
-      <c r="F96" s="17"/>
-      <c r="G96" s="17"/>
-      <c r="H96" s="17"/>
-      <c r="I96" s="17"/>
-      <c r="J96" s="17"/>
-      <c r="K96" s="17"/>
+      <c r="A96" s="15"/>
+      <c r="B96" s="15"/>
+      <c r="C96" s="15"/>
+      <c r="D96" s="15"/>
+      <c r="E96" s="15"/>
+      <c r="F96" s="15"/>
+      <c r="G96" s="15"/>
+      <c r="H96" s="15"/>
+      <c r="I96" s="15"/>
+      <c r="J96" s="15"/>
+      <c r="K96" s="15"/>
     </row>
     <row r="97" spans="1:11">
-      <c r="A97" s="17"/>
-      <c r="B97" s="17"/>
-      <c r="C97" s="17"/>
-      <c r="D97" s="17"/>
-      <c r="E97" s="17"/>
-      <c r="F97" s="17"/>
-      <c r="G97" s="17"/>
-      <c r="H97" s="17"/>
-      <c r="I97" s="17"/>
-      <c r="J97" s="17"/>
-      <c r="K97" s="17"/>
+      <c r="A97" s="15"/>
+      <c r="B97" s="15"/>
+      <c r="C97" s="15"/>
+      <c r="D97" s="15"/>
+      <c r="E97" s="15"/>
+      <c r="F97" s="15"/>
+      <c r="G97" s="15"/>
+      <c r="H97" s="15"/>
+      <c r="I97" s="15"/>
+      <c r="J97" s="15"/>
+      <c r="K97" s="15"/>
     </row>
     <row r="98" spans="1:11">
-      <c r="A98" s="17"/>
-      <c r="B98" s="17"/>
-      <c r="C98" s="17"/>
-      <c r="D98" s="17"/>
-      <c r="E98" s="17"/>
-      <c r="F98" s="17"/>
-      <c r="G98" s="17"/>
-      <c r="H98" s="17"/>
-      <c r="I98" s="17"/>
-      <c r="J98" s="17"/>
-      <c r="K98" s="17"/>
+      <c r="A98" s="15"/>
+      <c r="B98" s="15"/>
+      <c r="C98" s="15"/>
+      <c r="D98" s="15"/>
+      <c r="E98" s="15"/>
+      <c r="F98" s="15"/>
+      <c r="G98" s="15"/>
+      <c r="H98" s="15"/>
+      <c r="I98" s="15"/>
+      <c r="J98" s="15"/>
+      <c r="K98" s="15"/>
     </row>
     <row r="99" spans="1:11">
-      <c r="A99" s="17"/>
-      <c r="B99" s="17"/>
-      <c r="C99" s="17"/>
-      <c r="D99" s="17"/>
-      <c r="E99" s="17"/>
-      <c r="F99" s="17"/>
-      <c r="G99" s="17"/>
-      <c r="H99" s="17"/>
-      <c r="I99" s="17"/>
-      <c r="J99" s="17"/>
-      <c r="K99" s="17"/>
-    </row>
-    <row r="100" spans="1:11">
-      <c r="A100" s="17"/>
-      <c r="B100" s="17"/>
-      <c r="C100" s="17"/>
-      <c r="D100" s="17"/>
-      <c r="E100" s="17"/>
-      <c r="F100" s="17"/>
-      <c r="G100" s="17"/>
-      <c r="H100" s="17"/>
-      <c r="I100" s="17"/>
-      <c r="J100" s="17"/>
-      <c r="K100" s="17"/>
+      <c r="A99" s="15"/>
+      <c r="B99" s="15"/>
+      <c r="C99" s="15"/>
+      <c r="D99" s="15"/>
+      <c r="E99" s="15"/>
+      <c r="F99" s="15"/>
+      <c r="G99" s="15"/>
+      <c r="H99" s="15"/>
+      <c r="I99" s="15"/>
+      <c r="J99" s="15"/>
+      <c r="K99" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A6:A15"/>
-    <mergeCell ref="A16:A31"/>
-    <mergeCell ref="A32:A34"/>
-    <mergeCell ref="A35:A40"/>
-    <mergeCell ref="A41:A61"/>
+    <mergeCell ref="A6:A14"/>
+    <mergeCell ref="A15:A29"/>
+    <mergeCell ref="A30:A32"/>
+    <mergeCell ref="A33:A38"/>
+    <mergeCell ref="A39:A59"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
@@ -5203,7 +4742,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:K100"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="27" style="1" customWidth="1"/>
     <col min="2" max="2" width="22" style="1" customWidth="1"/>
@@ -5215,7 +4754,7 @@
   <sheetData>
     <row r="1" ht="16.8" customHeight="1" spans="1:11">
       <c r="A1" s="2" t="s">
-        <v>309</v>
+        <v>294</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -5243,19 +4782,19 @@
     </row>
     <row r="3" ht="15" customHeight="1" spans="1:11">
       <c r="A3" s="4" t="s">
-        <v>310</v>
+        <v>295</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>311</v>
+        <v>296</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>6</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>312</v>
+        <v>297</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>313</v>
+        <v>298</v>
       </c>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
@@ -5269,16 +4808,16 @@
         <v>49</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>314</v>
+        <v>299</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>315</v>
+        <v>300</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>316</v>
+        <v>301</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>317</v>
+        <v>302</v>
       </c>
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
@@ -5292,16 +4831,16 @@
         <v>49</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>318</v>
+        <v>303</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>319</v>
+        <v>304</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>316</v>
+        <v>301</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>320</v>
+        <v>305</v>
       </c>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
@@ -5315,16 +4854,16 @@
         <v>49</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>321</v>
+        <v>306</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>322</v>
+        <v>307</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>316</v>
+        <v>301</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>323</v>
+        <v>308</v>
       </c>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
@@ -5338,16 +4877,16 @@
         <v>49</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>324</v>
+        <v>309</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>325</v>
+        <v>310</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>316</v>
+        <v>301</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>326</v>
+        <v>311</v>
       </c>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
@@ -5361,16 +4900,16 @@
         <v>49</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>327</v>
+        <v>312</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>328</v>
+        <v>313</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>316</v>
+        <v>301</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>320</v>
+        <v>305</v>
       </c>
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
@@ -5387,13 +4926,13 @@
         <v>119</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>329</v>
+        <v>314</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>330</v>
+        <v>315</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>331</v>
+        <v>316</v>
       </c>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
@@ -5407,16 +4946,16 @@
         <v>57</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>332</v>
+        <v>317</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>330</v>
+        <v>315</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>331</v>
+        <v>316</v>
       </c>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
@@ -5430,16 +4969,16 @@
         <v>57</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>333</v>
+        <v>318</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>330</v>
+        <v>315</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>331</v>
+        <v>316</v>
       </c>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
@@ -5450,19 +4989,19 @@
     </row>
     <row r="12" ht="15" customHeight="1" spans="1:11">
       <c r="A12" s="7" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>334</v>
+        <v>312</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>335</v>
+        <v>319</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>336</v>
+        <v>315</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>337</v>
+        <v>316</v>
       </c>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
@@ -5473,19 +5012,19 @@
     </row>
     <row r="13" ht="15" customHeight="1" spans="1:11">
       <c r="A13" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>338</v>
+        <v>135</v>
+      </c>
+      <c r="B13" s="8">
+        <v>0</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>339</v>
+        <v>320</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>336</v>
+        <v>321</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>337</v>
+        <v>322</v>
       </c>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
@@ -5496,19 +5035,19 @@
     </row>
     <row r="14" ht="15" customHeight="1" spans="1:11">
       <c r="A14" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>340</v>
+        <v>135</v>
+      </c>
+      <c r="B14" s="8">
+        <v>1</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>341</v>
+        <v>323</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>336</v>
+        <v>321</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>337</v>
+        <v>322</v>
       </c>
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
@@ -5519,19 +5058,19 @@
     </row>
     <row r="15" ht="15" customHeight="1" spans="1:11">
       <c r="A15" s="7" t="s">
-        <v>64</v>
+        <v>158</v>
       </c>
       <c r="B15" s="8" t="s">
+        <v>324</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>326</v>
+      </c>
+      <c r="E15" s="9" t="s">
         <v>327</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>342</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>337</v>
       </c>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
@@ -5542,19 +5081,19 @@
     </row>
     <row r="16" ht="15" customHeight="1" spans="1:11">
       <c r="A16" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="B16" s="8">
-        <v>0</v>
+        <v>158</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>328</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>343</v>
+        <v>329</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>344</v>
+        <v>326</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
@@ -5565,19 +5104,19 @@
     </row>
     <row r="17" ht="15" customHeight="1" spans="1:11">
       <c r="A17" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="B17" s="8">
-        <v>1</v>
+        <v>158</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>330</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>345</v>
+        <v>331</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>344</v>
+        <v>326</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
@@ -5588,19 +5127,19 @@
     </row>
     <row r="18" ht="15" customHeight="1" spans="1:11">
       <c r="A18" s="7" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>346</v>
+        <v>332</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>347</v>
+        <v>333</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>348</v>
+        <v>326</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>349</v>
+        <v>327</v>
       </c>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
@@ -5611,19 +5150,19 @@
     </row>
     <row r="19" ht="15" customHeight="1" spans="1:11">
       <c r="A19" s="7" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>350</v>
+        <v>334</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>351</v>
+        <v>335</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>348</v>
+        <v>326</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>349</v>
+        <v>327</v>
       </c>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
@@ -5633,21 +5172,11 @@
       <c r="K19" s="3"/>
     </row>
     <row r="20" ht="15" customHeight="1" spans="1:11">
-      <c r="A20" s="7" t="s">
-        <v>172</v>
-      </c>
-      <c r="B20" s="8" t="s">
-        <v>352</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>353</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>348</v>
-      </c>
-      <c r="E20" s="9" t="s">
-        <v>349</v>
-      </c>
+      <c r="A20" s="7"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="9"/>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
@@ -5656,21 +5185,11 @@
       <c r="K20" s="3"/>
     </row>
     <row r="21" ht="15" customHeight="1" spans="1:11">
-      <c r="A21" s="7" t="s">
-        <v>172</v>
-      </c>
-      <c r="B21" s="8" t="s">
-        <v>354</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>355</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>348</v>
-      </c>
-      <c r="E21" s="9" t="s">
-        <v>349</v>
-      </c>
+      <c r="A21" s="7"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="9"/>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
@@ -5680,20 +5199,12 @@
     </row>
     <row r="22" ht="15" customHeight="1" spans="1:11">
       <c r="A22" s="7" t="s">
-        <v>172</v>
-      </c>
-      <c r="B22" s="10" t="s">
-        <v>356</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>357</v>
-      </c>
-      <c r="D22" s="10" t="s">
-        <v>348</v>
-      </c>
-      <c r="E22" s="9" t="s">
-        <v>349</v>
-      </c>
+        <v>336</v>
+      </c>
+      <c r="B22" s="10"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="10"/>
+      <c r="E22" s="9"/>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
@@ -5715,11 +5226,21 @@
       <c r="K23" s="3"/>
     </row>
     <row r="24" ht="15" customHeight="1" spans="1:11">
-      <c r="A24" s="3"/>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
+      <c r="A24" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>341</v>
+      </c>
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
@@ -5728,13 +5249,21 @@
       <c r="K24" s="3"/>
     </row>
     <row r="25" ht="15" customHeight="1" spans="1:11">
-      <c r="A25" s="11" t="s">
-        <v>358</v>
-      </c>
-      <c r="B25" s="11"/>
-      <c r="C25" s="11"/>
-      <c r="D25" s="11"/>
-      <c r="E25" s="11"/>
+      <c r="A25" s="11">
+        <v>1</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>342</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>343</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="E25" s="11" t="s">
+        <v>344</v>
+      </c>
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
@@ -5743,11 +5272,21 @@
       <c r="K25" s="3"/>
     </row>
     <row r="26" ht="15" customHeight="1" spans="1:11">
-      <c r="A26" s="3"/>
-      <c r="B26" s="3"/>
-      <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
+      <c r="A26" s="3">
+        <v>2</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>301</v>
+      </c>
       <c r="F26" s="3"/>
       <c r="G26" s="3"/>
       <c r="H26" s="3"/>
@@ -5756,20 +5295,20 @@
       <c r="K26" s="3"/>
     </row>
     <row r="27" ht="15" customHeight="1" spans="1:11">
-      <c r="A27" s="4" t="s">
-        <v>359</v>
+      <c r="A27" s="4">
+        <v>3</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>360</v>
+        <v>347</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>361</v>
+        <v>348</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>362</v>
+        <v>177</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>363</v>
+        <v>349</v>
       </c>
       <c r="F27" s="3"/>
       <c r="G27" s="3"/>
@@ -5778,21 +5317,21 @@
       <c r="J27" s="3"/>
       <c r="K27" s="3"/>
     </row>
-    <row r="28" ht="25.5" spans="1:11">
+    <row r="28" ht="39.6" spans="1:11">
       <c r="A28" s="7">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>364</v>
+        <v>350</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>365</v>
+        <v>351</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>57</v>
+        <v>352</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>366</v>
+        <v>353</v>
       </c>
       <c r="F28" s="3"/>
       <c r="G28" s="3"/>
@@ -5801,21 +5340,21 @@
       <c r="J28" s="3"/>
       <c r="K28" s="3"/>
     </row>
-    <row r="29" ht="51" spans="1:11">
+    <row r="29" ht="39.6" spans="1:11">
       <c r="A29" s="7">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>49</v>
+        <v>177</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>316</v>
+        <v>356</v>
       </c>
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
@@ -5824,22 +5363,12 @@
       <c r="J29" s="3"/>
       <c r="K29" s="3"/>
     </row>
-    <row r="30" ht="25.5" spans="1:11">
-      <c r="A30" s="7">
-        <v>3</v>
-      </c>
-      <c r="B30" s="8" t="s">
-        <v>369</v>
-      </c>
-      <c r="C30" s="8" t="s">
-        <v>370</v>
-      </c>
-      <c r="D30" s="10" t="s">
-        <v>371</v>
-      </c>
-      <c r="E30" s="9" t="s">
-        <v>372</v>
-      </c>
+    <row r="30" spans="1:11">
+      <c r="A30"/>
+      <c r="B30"/>
+      <c r="C30"/>
+      <c r="D30"/>
+      <c r="E30"/>
       <c r="F30" s="3"/>
       <c r="G30" s="3"/>
       <c r="H30" s="3"/>
@@ -5847,22 +5376,12 @@
       <c r="J30" s="3"/>
       <c r="K30" s="3"/>
     </row>
-    <row r="31" ht="38.25" spans="1:11">
-      <c r="A31" s="7">
-        <v>4</v>
-      </c>
-      <c r="B31" s="8" t="s">
-        <v>373</v>
-      </c>
-      <c r="C31" s="8" t="s">
-        <v>374</v>
-      </c>
-      <c r="D31" s="8" t="s">
-        <v>375</v>
-      </c>
-      <c r="E31" s="9" t="s">
-        <v>376</v>
-      </c>
+    <row r="31" spans="1:11">
+      <c r="A31"/>
+      <c r="B31"/>
+      <c r="C31"/>
+      <c r="D31"/>
+      <c r="E31"/>
       <c r="F31" s="3"/>
       <c r="G31" s="3"/>
       <c r="H31" s="3"/>
@@ -5870,22 +5389,12 @@
       <c r="J31" s="3"/>
       <c r="K31" s="3"/>
     </row>
-    <row r="32" ht="38.25" spans="1:11">
-      <c r="A32" s="12">
-        <v>5</v>
-      </c>
-      <c r="B32" s="10" t="s">
-        <v>377</v>
-      </c>
-      <c r="C32" s="10" t="s">
-        <v>378</v>
-      </c>
-      <c r="D32" s="10" t="s">
-        <v>371</v>
-      </c>
-      <c r="E32" s="13" t="s">
-        <v>379</v>
-      </c>
+    <row r="32" spans="1:11">
+      <c r="A32"/>
+      <c r="B32"/>
+      <c r="C32"/>
+      <c r="D32"/>
+      <c r="E32"/>
       <c r="F32" s="3"/>
       <c r="G32" s="3"/>
       <c r="H32" s="3"/>
@@ -6780,7 +6289,7 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A22:E22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
